--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -11,15 +11,24 @@
     <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="seasons">Lists!$A$2:$A$7</definedName>
-    <definedName name="categories">Lists!$B$2:$B$6</definedName>
-    <definedName name="adv">Lists!$C$2:$C$5</definedName>
-    <definedName name="col">Lists!$D$2:$D$6</definedName>
-    <definedName name="edi">Lists!$E$2:$E$10</definedName>
-    <definedName name="inv">Lists!$F$2:$F$3</definedName>
-    <definedName name="eph">Lists!$G$2:$G$5</definedName>
-    <definedName name="desc_adv">Lists!$H$2:$H$9</definedName>
-    <definedName name="desc_col">Lists!$I$2:$I$4</definedName>
+    <definedName name="years">Lists!$A$2:$A$60</definedName>
+    <definedName name="seasons">Lists!$B$2:$B$7</definedName>
+    <definedName name="categories">Lists!$C$2:$C$6</definedName>
+    <definedName name="adv">Lists!$D$2:$D$5</definedName>
+    <definedName name="col">Lists!$E$2:$E$6</definedName>
+    <definedName name="edi">Lists!$F$2:$F$10</definedName>
+    <definedName name="inv">Lists!$G$2:$G$3</definedName>
+    <definedName name="eph">Lists!$H$2:$H$5</definedName>
+    <definedName name="desc_adv">Lists!$I$2:$I$9</definedName>
+    <definedName name="desc_col">Lists!$J$2:$J$4</definedName>
+    <definedName name="fragrance">Lists!$K$2:$K$13</definedName>
+    <definedName name="jeans">Lists!$L$2:$L$5</definedName>
+    <definedName name="underwear">Lists!$M$2:$M$4</definedName>
+    <definedName name="eyewear">Lists!$N$2:$N$2</definedName>
+    <definedName name="denim">Lists!$O$2:$O$2</definedName>
+    <definedName name="accessories">Lists!$P$2:$P$2</definedName>
+    <definedName name="shoes">Lists!$Q$2:$Q$2</definedName>
+    <definedName name="rtw">Lists!$R$2:$R$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +443,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -588,7 +597,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=years</formula1>
+    </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=seasons</formula1>
     </dataValidation>
@@ -601,6 +613,9 @@
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=INDIRECT("desc_"&amp;$D2)</formula1>
     </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=INDIRECT(SUBSTITUTE($G2," ","_"))</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -612,301 +627,861 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>seasons</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>adv</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>col</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inv</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>eph</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>desc_adv</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>desc_col</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fragrance</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>denim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>shoes</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rtw</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>ss</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>adv</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>print</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>rtw-w</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>vogue-us</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>show</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>backstage</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>fragrance</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>runway</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>obsession</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>are you wearing any</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ck underwear</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ck eyewear</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ck denim</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ck accessories</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ck shoes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ck rtw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>fw</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>col</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ooh</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>rtw-m</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>vogue-it</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>fitting</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>jeans</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>lookbook</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>eternity</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>nothing comes between me</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>my calvins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>aw</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>couture</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>vogue-paris</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>bts</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>underwear</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>catalog</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ck one</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>just the way you are</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i __ my calvins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>cruise</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>inv</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>denim</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>harpers</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>portrait</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>eyewear</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>escape</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ck jeans</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>pre-fall</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>eph</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>underwear</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>iD</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>denim</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>contradiction</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>resort</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>dazed</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>accessories</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>truth</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="E8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>interview</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>shoes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>be</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="E9" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>wmag</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>rtw</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>euphoria</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="E10" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>numero</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ck2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>eternity moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ck all</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
     </row>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -29,6 +29,19 @@
     <definedName name="accessories">Lists!$P$2:$P$2</definedName>
     <definedName name="shoes">Lists!$Q$2:$Q$2</definedName>
     <definedName name="rtw">Lists!$R$2:$R$2</definedName>
+    <definedName name="photographers">Lists!$S$2:$S$31</definedName>
+    <definedName name="directors">Lists!$T$2:$T$16</definedName>
+    <definedName name="models">Lists!$U$2:$U$27</definedName>
+    <definedName name="stylists">Lists!$V$2:$V$13</definedName>
+    <definedName name="hair_list">Lists!$W$2:$W$10</definedName>
+    <definedName name="makeup_list">Lists!$X$2:$X$11</definedName>
+    <definedName name="art_directors">Lists!$Y$2:$Y$6</definedName>
+    <definedName name="creative_directors">Lists!$Z$2:$Z$8</definedName>
+    <definedName name="set_designers">Lists!$AA$2:$AA$6</definedName>
+    <definedName name="casting_directors">Lists!$AB$2:$AB$6</definedName>
+    <definedName name="production_companies">Lists!$AC$2:$AC$7</definedName>
+    <definedName name="agencies">Lists!$AD$2:$AD$7</definedName>
+    <definedName name="publications">Lists!$AE$2:$AE$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -441,27 +454,26 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,129 +504,163 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>venue</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>campaign</t>
+          <t>photographer</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>photographer</t>
+          <t>director</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>director</t>
+          <t>producer</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>producer</t>
+          <t>production_company</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>production_company</t>
+          <t>model</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>stylist</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>stylist</t>
+          <t>art_director</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>art_director</t>
+          <t>creative_director</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>creative_director</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>set_designer</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>set_designer</t>
+          <t>casting_director</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>casting_director</t>
+          <t>agency</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>agency</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>issue_date</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>issue_date</t>
+          <t>music</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="19">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=years</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=seasons</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=categories</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=photographers</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=directors</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=models</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=stylists</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=hair_list</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=makeup_list</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=art_directors</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=creative_directors</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=set_designers</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=casting_directors</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=production_companies</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=agencies</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=publications</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=INDIRECT("desc_"&amp;$D2)</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT(SUBSTITUTE($G2," ","_"))</formula1>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=INDIRECT(SUBSTITUTE($F2," ","_"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -627,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +767,71 @@
           <t>rtw</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>photographers</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>directors</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>stylists</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>hair_list</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>makeup_list</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>art_directors</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>creative_directors</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>set_designers</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>casting_directors</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>production_companies</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>agencies</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>publications</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -813,6 +924,71 @@
           <t>ck rtw</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Bruce Weber</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Fabien Baron</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Kate Moss</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Camilla Nickerson</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Garren</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Pat McGrath</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Fabien Baron</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Calvin Klein</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Stefan Beckman</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>James Scully</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Baron &amp; Baron</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Baron &amp; Baron</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Vogue US</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -880,6 +1056,71 @@
           <t>my calvins</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Steven Meisel</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>David Fincher</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Christy Turlington</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Joe McKenna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Guido Palau</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Diane Kendal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Sam Shahid</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Raf Simons</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mary Howard</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Piergiorgio Del Moro</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Vogue Italia</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -942,6 +1183,71 @@
           <t>i __ my calvins</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Richard Avedon</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Bruce Weber</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Naomi Campbell</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Karl Templer</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sam McKnight</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaron de Mey</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Tibor Kalman</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Francisco Costa</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Andy Hillman</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Ashley Brokaw</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Calvin Klein Inc.</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Wieden+Kennedy</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Vogue Paris</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -994,6 +1300,71 @@
           <t>ck jeans</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Herb Ritts</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Sofia Coppola</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Cindy Crawford</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Marie-Amélie Sauvé</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Eugene Souleiman</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Tom Pecheux</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Neville Brody</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Italo Zucchelli</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Piers Hanmer</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Jess Hallett</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hungry Man</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Harper's Bazaar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1031,6 +1402,71 @@
           <t>contradiction</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Patrick Demarchelier</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Mario Sorrenti</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linda Evangelista</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Olivier Rizzo</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Christiaan Houtenbos</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>François Nars</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Peter Saville</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Kevin Carrigan</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Jack Flanagan</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Anita Bitton</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>RSA Films</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Laird+Partners</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>i-D</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1058,6 +1494,56 @@
           <t>truth</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Mario Sorrenti</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Steven Meisel</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Brooke Shields</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Alastair McKimm</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Didier Malige</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Kevyn Aucoin</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Pieter Mulier</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Anonymous Content</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>CKX</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Dazed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1080,6 +1566,46 @@
           <t>be</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>David Sims</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Herb Ritts</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mark Wahlberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lucinda Chambers</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Julien d'Ys</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Linda Cantello</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Veronica Leoni</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1102,6 +1628,41 @@
           <t>euphoria</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Mert &amp; Marcus</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Spike Jonze</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Travis Fimmel</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Carlyne Cerf de Dudzeele</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Anthony Turner</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Charlotte Tilbury</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>W Magazine</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1119,6 +1680,41 @@
           <t>ck2</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Steven Klein</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Tony Kaye</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lara Stone</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Grace Coddington</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Duffy</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Lucia Pieroni</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Numéro</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1131,6 +1727,36 @@
           <t>eternity moment</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Inez &amp; Vinoodh</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jonas Åkerlund</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Natalia Vodianova</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Carine Roitfeld</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Peter Philips</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Self Service</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1143,6 +1769,31 @@
           <t>free</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Mario Testino</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Mark Romanek</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jamie Dornan</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Melanie Ward</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1155,6 +1806,31 @@
           <t>ck all</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Glen Luchford</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Floria Sigismondi</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gisele Bündchen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Tonne Goodman</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Another</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1162,6 +1838,26 @@
           <t>1980</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Craig McDean</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Steven Klein</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jessica Stam</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>The Face</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1169,6 +1865,26 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Willy Vanderperre</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Mert &amp; Marcus</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Daria Werbowy</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>AnOther Man</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1176,6 +1892,26 @@
           <t>1982</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Fabien Baron</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Sam Taylor-Johnson</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Edie Campbell</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>GQ</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1183,6 +1919,21 @@
           <t>1983</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Peter Lindbergh</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Anna Ewers</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Vanity Fair</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1190,6 +1941,16 @@
           <t>1984</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Helmut Newton</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Saskia de Brauw</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1197,6 +1958,16 @@
           <t>1985</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Annie Leibovitz</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Justin Bieber</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1204,6 +1975,16 @@
           <t>1986</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Nick Knight</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kendall Jenner</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1211,6 +1992,16 @@
           <t>1987</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Juergen Teller</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bella Hadid</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1218,6 +2009,16 @@
           <t>1988</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Tyrone Lebon</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lily-Rose Depp</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1225,6 +2026,16 @@
           <t>1989</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Lachlan Bailey</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>FKA twigs</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1232,6 +2043,16 @@
           <t>1990</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Cass Bird</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1239,6 +2060,16 @@
           <t>1991</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Harley Weir</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>A$AP Rocky</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1246,6 +2077,16 @@
           <t>1992</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Daniel Jackson</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kaia Gerber</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1253,6 +2094,16 @@
           <t>1993</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Niall McInerney</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jeremy Allen White</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1260,6 +2111,11 @@
           <t>1994</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Sølve Sundsbø</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1267,6 +2123,11 @@
           <t>1995</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Paolo Roversi</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1274,11 +2135,21 @@
           <t>1996</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Collier Schorr</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>1997</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Ethan James Green</t>
         </is>
       </c>
     </row>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -11,37 +11,37 @@
     <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="years">Lists!$A$2:$A$60</definedName>
-    <definedName name="seasons">Lists!$B$2:$B$7</definedName>
-    <definedName name="categories">Lists!$C$2:$C$6</definedName>
-    <definedName name="adv">Lists!$D$2:$D$5</definedName>
-    <definedName name="col">Lists!$E$2:$E$6</definedName>
-    <definedName name="edi">Lists!$F$2:$F$10</definedName>
-    <definedName name="inv">Lists!$G$2:$G$3</definedName>
-    <definedName name="eph">Lists!$H$2:$H$5</definedName>
-    <definedName name="desc_adv">Lists!$I$2:$I$9</definedName>
-    <definedName name="desc_col">Lists!$J$2:$J$4</definedName>
-    <definedName name="fragrance">Lists!$K$2:$K$13</definedName>
-    <definedName name="jeans">Lists!$L$2:$L$5</definedName>
-    <definedName name="underwear">Lists!$M$2:$M$4</definedName>
-    <definedName name="eyewear">Lists!$N$2:$N$2</definedName>
-    <definedName name="denim">Lists!$O$2:$O$2</definedName>
-    <definedName name="accessories">Lists!$P$2:$P$2</definedName>
-    <definedName name="shoes">Lists!$Q$2:$Q$2</definedName>
-    <definedName name="rtw">Lists!$R$2:$R$2</definedName>
-    <definedName name="photographers">Lists!$S$2:$S$31</definedName>
-    <definedName name="directors">Lists!$T$2:$T$16</definedName>
-    <definedName name="models">Lists!$U$2:$U$27</definedName>
-    <definedName name="stylists">Lists!$V$2:$V$13</definedName>
-    <definedName name="hair_list">Lists!$W$2:$W$10</definedName>
-    <definedName name="makeup_list">Lists!$X$2:$X$11</definedName>
-    <definedName name="art_directors">Lists!$Y$2:$Y$6</definedName>
-    <definedName name="creative_directors">Lists!$Z$2:$Z$8</definedName>
-    <definedName name="set_designers">Lists!$AA$2:$AA$6</definedName>
-    <definedName name="casting_directors">Lists!$AB$2:$AB$6</definedName>
-    <definedName name="production_companies">Lists!$AC$2:$AC$7</definedName>
-    <definedName name="agencies">Lists!$AD$2:$AD$7</definedName>
-    <definedName name="publications">Lists!$AE$2:$AE$17</definedName>
+    <definedName name="years">OFFSET(Lists!$A$2,0,0,COUNTA(Lists!$A:$A)-1,1)</definedName>
+    <definedName name="seasons">OFFSET(Lists!$B$2,0,0,COUNTA(Lists!$B:$B)-1,1)</definedName>
+    <definedName name="categories">OFFSET(Lists!$C$2,0,0,COUNTA(Lists!$C:$C)-1,1)</definedName>
+    <definedName name="adv">OFFSET(Lists!$D$2,0,0,COUNTA(Lists!$D:$D)-1,1)</definedName>
+    <definedName name="col">OFFSET(Lists!$E$2,0,0,COUNTA(Lists!$E:$E)-1,1)</definedName>
+    <definedName name="edi">OFFSET(Lists!$F$2,0,0,COUNTA(Lists!$F:$F)-1,1)</definedName>
+    <definedName name="inv">OFFSET(Lists!$G$2,0,0,COUNTA(Lists!$G:$G)-1,1)</definedName>
+    <definedName name="eph">OFFSET(Lists!$H$2,0,0,COUNTA(Lists!$H:$H)-1,1)</definedName>
+    <definedName name="desc_adv">OFFSET(Lists!$I$2,0,0,COUNTA(Lists!$I:$I)-1,1)</definedName>
+    <definedName name="desc_col">OFFSET(Lists!$J$2,0,0,COUNTA(Lists!$J:$J)-1,1)</definedName>
+    <definedName name="fragrance">OFFSET(Lists!$K$2,0,0,COUNTA(Lists!$K:$K)-1,1)</definedName>
+    <definedName name="jeans">OFFSET(Lists!$L$2,0,0,COUNTA(Lists!$L:$L)-1,1)</definedName>
+    <definedName name="underwear">OFFSET(Lists!$M$2,0,0,COUNTA(Lists!$M:$M)-1,1)</definedName>
+    <definedName name="eyewear">OFFSET(Lists!$N$2,0,0,COUNTA(Lists!$N:$N)-1,1)</definedName>
+    <definedName name="denim">OFFSET(Lists!$O$2,0,0,COUNTA(Lists!$O:$O)-1,1)</definedName>
+    <definedName name="accessories">OFFSET(Lists!$P$2,0,0,COUNTA(Lists!$P:$P)-1,1)</definedName>
+    <definedName name="shoes">OFFSET(Lists!$Q$2,0,0,COUNTA(Lists!$Q:$Q)-1,1)</definedName>
+    <definedName name="rtw">OFFSET(Lists!$R$2,0,0,COUNTA(Lists!$R:$R)-1,1)</definedName>
+    <definedName name="photographers">OFFSET(Lists!$S$2,0,0,COUNTA(Lists!$S:$S)-1,1)</definedName>
+    <definedName name="directors">OFFSET(Lists!$T$2,0,0,COUNTA(Lists!$T:$T)-1,1)</definedName>
+    <definedName name="models">OFFSET(Lists!$U$2,0,0,COUNTA(Lists!$U:$U)-1,1)</definedName>
+    <definedName name="stylists">OFFSET(Lists!$V$2,0,0,COUNTA(Lists!$V:$V)-1,1)</definedName>
+    <definedName name="hair_list">OFFSET(Lists!$W$2,0,0,COUNTA(Lists!$W:$W)-1,1)</definedName>
+    <definedName name="makeup_list">OFFSET(Lists!$X$2,0,0,COUNTA(Lists!$X:$X)-1,1)</definedName>
+    <definedName name="art_directors">OFFSET(Lists!$Y$2,0,0,COUNTA(Lists!$Y:$Y)-1,1)</definedName>
+    <definedName name="creative_directors">OFFSET(Lists!$Z$2,0,0,COUNTA(Lists!$Z:$Z)-1,1)</definedName>
+    <definedName name="set_designers">OFFSET(Lists!$AA$2,0,0,COUNTA(Lists!$AA:$AA)-1,1)</definedName>
+    <definedName name="casting_directors">OFFSET(Lists!$AB$2,0,0,COUNTA(Lists!$AB:$AB)-1,1)</definedName>
+    <definedName name="production_companies">OFFSET(Lists!$AC$2,0,0,COUNTA(Lists!$AC:$AC)-1,1)</definedName>
+    <definedName name="agencies">OFFSET(Lists!$AD$2,0,0,COUNTA(Lists!$AD:$AD)-1,1)</definedName>
+    <definedName name="publications">OFFSET(Lists!$AE$2,0,0,COUNTA(Lists!$AE:$AE)-1,1)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1722,6 +1722,11 @@
           <t>1977</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>theface</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>eternity moment</t>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -834,10 +834,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1968</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -991,10 +989,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1969</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1123,10 +1119,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1970</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1250,10 +1244,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1971</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1367,10 +1359,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1972</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1469,10 +1459,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
+      <c r="A7" t="n">
+        <v>1973</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1546,10 +1534,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
+      <c r="A8" t="n">
+        <v>1974</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1608,10 +1594,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1975</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,10 +1649,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1717,10 +1699,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,10 +1744,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1978</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1801,10 +1779,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1979</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1838,10 +1814,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1980</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1865,10 +1839,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1981</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1892,10 +1864,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1982</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1919,10 +1889,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1983</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -1941,10 +1909,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1984</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -1958,10 +1924,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1985</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -1975,10 +1939,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1986</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -1992,10 +1954,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1987</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2009,10 +1969,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1988</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2026,10 +1984,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1989</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2043,10 +1999,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1990</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2060,10 +2014,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1991</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2077,10 +2029,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1992</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2094,10 +2044,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1993</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2111,10 +2059,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
+      <c r="A28" t="n">
+        <v>1994</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2123,10 +2069,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
+      <c r="A29" t="n">
+        <v>1995</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2135,10 +2079,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
+      <c r="A30" t="n">
+        <v>1996</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -2147,10 +2089,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
+      <c r="A31" t="n">
+        <v>1997</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2159,206 +2099,148 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
+      <c r="A32" t="n">
+        <v>1998</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
+      <c r="A33" t="n">
+        <v>1999</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+      <c r="A34" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
+      <c r="A35" t="n">
+        <v>2001</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="A36" t="n">
+        <v>2002</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="A37" t="n">
+        <v>2003</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="A38" t="n">
+        <v>2004</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="A39" t="n">
+        <v>2005</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="A40" t="n">
+        <v>2006</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+      <c r="A41" t="n">
+        <v>2007</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="A42" t="n">
+        <v>2008</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+      <c r="A43" t="n">
+        <v>2009</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="A44" t="n">
+        <v>2010</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A45" t="n">
+        <v>2011</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A46" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A47" t="n">
+        <v>2013</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A48" t="n">
+        <v>2014</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="A49" t="n">
+        <v>2015</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="A50" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
+      <c r="A51" t="n">
+        <v>2017</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="A52" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="A53" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="A54" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="A55" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="A56" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A57" t="n">
+        <v>2023</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A58" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A59" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="A60" t="n">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -11,37 +11,37 @@
     <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="years">OFFSET(Lists!$A$2,0,0,COUNTA(Lists!$A:$A)-1,1)</definedName>
-    <definedName name="seasons">OFFSET(Lists!$B$2,0,0,COUNTA(Lists!$B:$B)-1,1)</definedName>
-    <definedName name="categories">OFFSET(Lists!$C$2,0,0,COUNTA(Lists!$C:$C)-1,1)</definedName>
-    <definedName name="adv">OFFSET(Lists!$D$2,0,0,COUNTA(Lists!$D:$D)-1,1)</definedName>
-    <definedName name="col">OFFSET(Lists!$E$2,0,0,COUNTA(Lists!$E:$E)-1,1)</definedName>
-    <definedName name="edi">OFFSET(Lists!$F$2,0,0,COUNTA(Lists!$F:$F)-1,1)</definedName>
-    <definedName name="inv">OFFSET(Lists!$G$2,0,0,COUNTA(Lists!$G:$G)-1,1)</definedName>
-    <definedName name="eph">OFFSET(Lists!$H$2,0,0,COUNTA(Lists!$H:$H)-1,1)</definedName>
-    <definedName name="desc_adv">OFFSET(Lists!$I$2,0,0,COUNTA(Lists!$I:$I)-1,1)</definedName>
-    <definedName name="desc_col">OFFSET(Lists!$J$2,0,0,COUNTA(Lists!$J:$J)-1,1)</definedName>
-    <definedName name="fragrance">OFFSET(Lists!$K$2,0,0,COUNTA(Lists!$K:$K)-1,1)</definedName>
-    <definedName name="jeans">OFFSET(Lists!$L$2,0,0,COUNTA(Lists!$L:$L)-1,1)</definedName>
-    <definedName name="underwear">OFFSET(Lists!$M$2,0,0,COUNTA(Lists!$M:$M)-1,1)</definedName>
-    <definedName name="eyewear">OFFSET(Lists!$N$2,0,0,COUNTA(Lists!$N:$N)-1,1)</definedName>
-    <definedName name="denim">OFFSET(Lists!$O$2,0,0,COUNTA(Lists!$O:$O)-1,1)</definedName>
-    <definedName name="accessories">OFFSET(Lists!$P$2,0,0,COUNTA(Lists!$P:$P)-1,1)</definedName>
-    <definedName name="shoes">OFFSET(Lists!$Q$2,0,0,COUNTA(Lists!$Q:$Q)-1,1)</definedName>
-    <definedName name="rtw">OFFSET(Lists!$R$2,0,0,COUNTA(Lists!$R:$R)-1,1)</definedName>
-    <definedName name="photographers">OFFSET(Lists!$S$2,0,0,COUNTA(Lists!$S:$S)-1,1)</definedName>
-    <definedName name="directors">OFFSET(Lists!$T$2,0,0,COUNTA(Lists!$T:$T)-1,1)</definedName>
-    <definedName name="models">OFFSET(Lists!$U$2,0,0,COUNTA(Lists!$U:$U)-1,1)</definedName>
-    <definedName name="stylists">OFFSET(Lists!$V$2,0,0,COUNTA(Lists!$V:$V)-1,1)</definedName>
-    <definedName name="hair_list">OFFSET(Lists!$W$2,0,0,COUNTA(Lists!$W:$W)-1,1)</definedName>
-    <definedName name="makeup_list">OFFSET(Lists!$X$2,0,0,COUNTA(Lists!$X:$X)-1,1)</definedName>
-    <definedName name="art_directors">OFFSET(Lists!$Y$2,0,0,COUNTA(Lists!$Y:$Y)-1,1)</definedName>
-    <definedName name="creative_directors">OFFSET(Lists!$Z$2,0,0,COUNTA(Lists!$Z:$Z)-1,1)</definedName>
-    <definedName name="set_designers">OFFSET(Lists!$AA$2,0,0,COUNTA(Lists!$AA:$AA)-1,1)</definedName>
-    <definedName name="casting_directors">OFFSET(Lists!$AB$2,0,0,COUNTA(Lists!$AB:$AB)-1,1)</definedName>
-    <definedName name="production_companies">OFFSET(Lists!$AC$2,0,0,COUNTA(Lists!$AC:$AC)-1,1)</definedName>
-    <definedName name="agencies">OFFSET(Lists!$AD$2,0,0,COUNTA(Lists!$AD:$AD)-1,1)</definedName>
-    <definedName name="publications">OFFSET(Lists!$AE$2,0,0,COUNTA(Lists!$AE:$AE)-1,1)</definedName>
+    <definedName name="years">tbl_years[years]</definedName>
+    <definedName name="seasons">tbl_seasons[seasons]</definedName>
+    <definedName name="categories">tbl_categories[categories]</definedName>
+    <definedName name="adv">tbl_adv[adv]</definedName>
+    <definedName name="col">tbl_col[col]</definedName>
+    <definedName name="edi">tbl_edi[edi]</definedName>
+    <definedName name="inv">tbl_inv[inv]</definedName>
+    <definedName name="eph">tbl_eph[eph]</definedName>
+    <definedName name="desc_adv">tbl_desc_adv[desc_adv]</definedName>
+    <definedName name="desc_col">tbl_desc_col[desc_col]</definedName>
+    <definedName name="fragrance">tbl_fragrance[fragrance]</definedName>
+    <definedName name="jeans">tbl_jeans[jeans]</definedName>
+    <definedName name="underwear">tbl_underwear[underwear]</definedName>
+    <definedName name="eyewear">tbl_eyewear[eyewear]</definedName>
+    <definedName name="denim">tbl_denim[denim]</definedName>
+    <definedName name="accessories">tbl_accessories[accessories]</definedName>
+    <definedName name="shoes">tbl_shoes[shoes]</definedName>
+    <definedName name="rtw">tbl_rtw[rtw]</definedName>
+    <definedName name="photographers">tbl_photographers[photographers]</definedName>
+    <definedName name="directors">tbl_directors[directors]</definedName>
+    <definedName name="models">tbl_models[models]</definedName>
+    <definedName name="stylists">tbl_stylists[stylists]</definedName>
+    <definedName name="hair_list">tbl_hair_list[hair_list]</definedName>
+    <definedName name="makeup_list">tbl_makeup_list[makeup_list]</definedName>
+    <definedName name="art_directors">tbl_art_directors[art_directors]</definedName>
+    <definedName name="creative_directors">tbl_creative_directors[creative_directors]</definedName>
+    <definedName name="set_designers">tbl_set_designers[set_designers]</definedName>
+    <definedName name="casting_directors">tbl_casting_directors[casting_directors]</definedName>
+    <definedName name="production_companies">tbl_production_companies[production_companies]</definedName>
+    <definedName name="agencies">tbl_agencies[agencies]</definedName>
+    <definedName name="publications">tbl_publications[publications]</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -155,6 +155,316 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_years" displayName="tbl_years" ref="A1:A60" headerRowCount="1">
+  <autoFilter ref="A1:A60"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="years"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl_desc_col" displayName="tbl_desc_col" ref="J1:J4" headerRowCount="1">
+  <autoFilter ref="J1:J4"/>
+  <tableColumns count="1">
+    <tableColumn id="10" name="desc_col"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_fragrance" displayName="tbl_fragrance" ref="K1:K13" headerRowCount="1">
+  <autoFilter ref="K1:K13"/>
+  <tableColumns count="1">
+    <tableColumn id="11" name="fragrance"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_jeans" displayName="tbl_jeans" ref="L1:L5" headerRowCount="1">
+  <autoFilter ref="L1:L5"/>
+  <tableColumns count="1">
+    <tableColumn id="12" name="jeans"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_underwear" displayName="tbl_underwear" ref="M1:M4" headerRowCount="1">
+  <autoFilter ref="M1:M4"/>
+  <tableColumns count="1">
+    <tableColumn id="13" name="underwear"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_eyewear" displayName="tbl_eyewear" ref="N1:N2" headerRowCount="1">
+  <autoFilter ref="N1:N2"/>
+  <tableColumns count="1">
+    <tableColumn id="14" name="eyewear"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_denim" displayName="tbl_denim" ref="O1:O2" headerRowCount="1">
+  <autoFilter ref="O1:O2"/>
+  <tableColumns count="1">
+    <tableColumn id="15" name="denim"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_accessories" displayName="tbl_accessories" ref="P1:P2" headerRowCount="1">
+  <autoFilter ref="P1:P2"/>
+  <tableColumns count="1">
+    <tableColumn id="16" name="accessories"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_shoes" displayName="tbl_shoes" ref="Q1:Q2" headerRowCount="1">
+  <autoFilter ref="Q1:Q2"/>
+  <tableColumns count="1">
+    <tableColumn id="17" name="shoes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_rtw" displayName="tbl_rtw" ref="R1:R2" headerRowCount="1">
+  <autoFilter ref="R1:R2"/>
+  <tableColumns count="1">
+    <tableColumn id="18" name="rtw"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_photographers" displayName="tbl_photographers" ref="S1:S31" headerRowCount="1">
+  <autoFilter ref="S1:S31"/>
+  <tableColumns count="1">
+    <tableColumn id="19" name="photographers"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_seasons" displayName="tbl_seasons" ref="B1:B7" headerRowCount="1">
+  <autoFilter ref="B1:B7"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="seasons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_directors" displayName="tbl_directors" ref="T1:T16" headerRowCount="1">
+  <autoFilter ref="T1:T16"/>
+  <tableColumns count="1">
+    <tableColumn id="20" name="directors"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_models" displayName="tbl_models" ref="U1:U27" headerRowCount="1">
+  <autoFilter ref="U1:U27"/>
+  <tableColumns count="1">
+    <tableColumn id="21" name="models"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_stylists" displayName="tbl_stylists" ref="V1:V13" headerRowCount="1">
+  <autoFilter ref="V1:V13"/>
+  <tableColumns count="1">
+    <tableColumn id="22" name="stylists"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_hair_list" displayName="tbl_hair_list" ref="W1:W10" headerRowCount="1">
+  <autoFilter ref="W1:W10"/>
+  <tableColumns count="1">
+    <tableColumn id="23" name="hair_list"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_makeup_list" displayName="tbl_makeup_list" ref="X1:X11" headerRowCount="1">
+  <autoFilter ref="X1:X11"/>
+  <tableColumns count="1">
+    <tableColumn id="24" name="makeup_list"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_art_directors" displayName="tbl_art_directors" ref="Y1:Y6" headerRowCount="1">
+  <autoFilter ref="Y1:Y6"/>
+  <tableColumns count="1">
+    <tableColumn id="25" name="art_directors"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_creative_directors" displayName="tbl_creative_directors" ref="Z1:Z8" headerRowCount="1">
+  <autoFilter ref="Z1:Z8"/>
+  <tableColumns count="1">
+    <tableColumn id="26" name="creative_directors"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_set_designers" displayName="tbl_set_designers" ref="AA1:AA6" headerRowCount="1">
+  <autoFilter ref="AA1:AA6"/>
+  <tableColumns count="1">
+    <tableColumn id="27" name="set_designers"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_casting_directors" displayName="tbl_casting_directors" ref="AB1:AB6" headerRowCount="1">
+  <autoFilter ref="AB1:AB6"/>
+  <tableColumns count="1">
+    <tableColumn id="28" name="casting_directors"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_production_companies" displayName="tbl_production_companies" ref="AC1:AC7" headerRowCount="1">
+  <autoFilter ref="AC1:AC7"/>
+  <tableColumns count="1">
+    <tableColumn id="29" name="production_companies"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_categories" displayName="tbl_categories" ref="C1:C6" headerRowCount="1">
+  <autoFilter ref="C1:C6"/>
+  <tableColumns count="1">
+    <tableColumn id="3" name="categories"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_agencies" displayName="tbl_agencies" ref="AD1:AD7" headerRowCount="1">
+  <autoFilter ref="AD1:AD7"/>
+  <tableColumns count="1">
+    <tableColumn id="30" name="agencies"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_publications" displayName="tbl_publications" ref="AE1:AE17" headerRowCount="1">
+  <autoFilter ref="AE1:AE17"/>
+  <tableColumns count="1">
+    <tableColumn id="31" name="publications"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl_adv" displayName="tbl_adv" ref="D1:D5" headerRowCount="1">
+  <autoFilter ref="D1:D5"/>
+  <tableColumns count="1">
+    <tableColumn id="4" name="adv"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl_col" displayName="tbl_col" ref="E1:E6" headerRowCount="1">
+  <autoFilter ref="E1:E6"/>
+  <tableColumns count="1">
+    <tableColumn id="5" name="col"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tbl_edi" displayName="tbl_edi" ref="F1:F11" headerRowCount="1">
+  <autoFilter ref="F1:F11"/>
+  <tableColumns count="1">
+    <tableColumn id="6" name="edi"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_inv" displayName="tbl_inv" ref="G1:G3" headerRowCount="1">
+  <autoFilter ref="G1:G3"/>
+  <tableColumns count="1">
+    <tableColumn id="7" name="inv"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_eph" displayName="tbl_eph" ref="H1:H5" headerRowCount="1">
+  <autoFilter ref="H1:H5"/>
+  <tableColumns count="1">
+    <tableColumn id="8" name="eph"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_desc_adv" displayName="tbl_desc_adv" ref="I1:I9" headerRowCount="1">
+  <autoFilter ref="I1:I9"/>
+  <tableColumns count="1">
+    <tableColumn id="9" name="desc_adv"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2245,5 +2555,38 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="31">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -2,48 +2,47 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Archive" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="years">tbl_years[years]</definedName>
-    <definedName name="seasons">tbl_seasons[seasons]</definedName>
+    <definedName name="accessories">tbl_accessories[accessories]</definedName>
+    <definedName name="adv">tbl_adv[adv]</definedName>
+    <definedName name="agencies">tbl_agencies[agencies]</definedName>
+    <definedName name="art_directors">tbl_art_directors[art_directors]</definedName>
+    <definedName name="casting_directors">tbl_casting_directors[casting_directors]</definedName>
     <definedName name="categories">tbl_categories[categories]</definedName>
-    <definedName name="adv">tbl_adv[adv]</definedName>
     <definedName name="col">tbl_col[col]</definedName>
-    <definedName name="edi">tbl_edi[edi]</definedName>
-    <definedName name="inv">tbl_inv[inv]</definedName>
-    <definedName name="eph">tbl_eph[eph]</definedName>
+    <definedName name="creative_directors">tbl_creative_directors[creative_directors]</definedName>
+    <definedName name="denim">tbl_denim[denim]</definedName>
     <definedName name="desc_adv">tbl_desc_adv[desc_adv]</definedName>
     <definedName name="desc_col">tbl_desc_col[desc_col]</definedName>
+    <definedName name="directors">tbl_directors[directors]</definedName>
+    <definedName name="edi">tbl_edi[edi]</definedName>
+    <definedName name="eph">tbl_eph[eph]</definedName>
+    <definedName name="eyewear">tbl_eyewear[eyewear]</definedName>
     <definedName name="fragrance">tbl_fragrance[fragrance]</definedName>
+    <definedName name="hair_list">tbl_hair_list[hair_list]</definedName>
+    <definedName name="inv">tbl_inv[inv]</definedName>
     <definedName name="jeans">tbl_jeans[jeans]</definedName>
+    <definedName name="makeup_list">tbl_makeup_list[makeup_list]</definedName>
+    <definedName name="models">tbl_models[models]</definedName>
+    <definedName name="photographers">tbl_photographers[photographers]</definedName>
+    <definedName name="production_companies">tbl_production_companies[production_companies]</definedName>
+    <definedName name="publications">tbl_publications[publications]</definedName>
+    <definedName name="rtw">tbl_rtw[rtw]</definedName>
+    <definedName name="seasons">tbl_seasons[seasons]</definedName>
+    <definedName name="set_designers">tbl_set_designers[set_designers]</definedName>
+    <definedName name="shoes">tbl_shoes[shoes]</definedName>
+    <definedName name="stylists">tbl_stylists[stylists]</definedName>
     <definedName name="underwear">tbl_underwear[underwear]</definedName>
-    <definedName name="eyewear">tbl_eyewear[eyewear]</definedName>
-    <definedName name="denim">tbl_denim[denim]</definedName>
-    <definedName name="accessories">tbl_accessories[accessories]</definedName>
-    <definedName name="shoes">tbl_shoes[shoes]</definedName>
-    <definedName name="rtw">tbl_rtw[rtw]</definedName>
-    <definedName name="photographers">tbl_photographers[photographers]</definedName>
-    <definedName name="directors">tbl_directors[directors]</definedName>
-    <definedName name="models">tbl_models[models]</definedName>
-    <definedName name="stylists">tbl_stylists[stylists]</definedName>
-    <definedName name="hair_list">tbl_hair_list[hair_list]</definedName>
-    <definedName name="makeup_list">tbl_makeup_list[makeup_list]</definedName>
-    <definedName name="art_directors">tbl_art_directors[art_directors]</definedName>
-    <definedName name="creative_directors">tbl_creative_directors[creative_directors]</definedName>
-    <definedName name="set_designers">tbl_set_designers[set_designers]</definedName>
-    <definedName name="casting_directors">tbl_casting_directors[casting_directors]</definedName>
-    <definedName name="production_companies">tbl_production_companies[production_companies]</definedName>
-    <definedName name="agencies">tbl_agencies[agencies]</definedName>
-    <definedName name="publications">tbl_publications[publications]</definedName>
+    <definedName name="years">tbl_years[years]</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -79,11 +78,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -163,7 +163,7 @@
   <tableColumns count="1">
     <tableColumn id="1" name="years"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -173,7 +173,7 @@
   <tableColumns count="1">
     <tableColumn id="10" name="desc_col"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -183,7 +183,7 @@
   <tableColumns count="1">
     <tableColumn id="11" name="fragrance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -193,7 +193,7 @@
   <tableColumns count="1">
     <tableColumn id="12" name="jeans"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -203,7 +203,7 @@
   <tableColumns count="1">
     <tableColumn id="13" name="underwear"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -213,7 +213,7 @@
   <tableColumns count="1">
     <tableColumn id="14" name="eyewear"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -223,7 +223,7 @@
   <tableColumns count="1">
     <tableColumn id="15" name="denim"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -233,7 +233,7 @@
   <tableColumns count="1">
     <tableColumn id="16" name="accessories"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -243,7 +243,7 @@
   <tableColumns count="1">
     <tableColumn id="17" name="shoes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -253,7 +253,7 @@
   <tableColumns count="1">
     <tableColumn id="18" name="rtw"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -263,7 +263,7 @@
   <tableColumns count="1">
     <tableColumn id="19" name="photographers"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -273,7 +273,7 @@
   <tableColumns count="1">
     <tableColumn id="2" name="seasons"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -283,7 +283,7 @@
   <tableColumns count="1">
     <tableColumn id="20" name="directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -293,7 +293,7 @@
   <tableColumns count="1">
     <tableColumn id="21" name="models"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -303,7 +303,7 @@
   <tableColumns count="1">
     <tableColumn id="22" name="stylists"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -313,7 +313,7 @@
   <tableColumns count="1">
     <tableColumn id="23" name="hair_list"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -323,7 +323,7 @@
   <tableColumns count="1">
     <tableColumn id="24" name="makeup_list"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -333,7 +333,7 @@
   <tableColumns count="1">
     <tableColumn id="25" name="art_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -343,7 +343,7 @@
   <tableColumns count="1">
     <tableColumn id="26" name="creative_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -353,7 +353,7 @@
   <tableColumns count="1">
     <tableColumn id="27" name="set_designers"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -363,7 +363,7 @@
   <tableColumns count="1">
     <tableColumn id="28" name="casting_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -373,7 +373,7 @@
   <tableColumns count="1">
     <tableColumn id="29" name="production_companies"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -383,7 +383,7 @@
   <tableColumns count="1">
     <tableColumn id="3" name="categories"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -393,7 +393,7 @@
   <tableColumns count="1">
     <tableColumn id="30" name="agencies"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -403,7 +403,7 @@
   <tableColumns count="1">
     <tableColumn id="31" name="publications"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -413,7 +413,7 @@
   <tableColumns count="1">
     <tableColumn id="4" name="adv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -423,7 +423,7 @@
   <tableColumns count="1">
     <tableColumn id="5" name="col"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -433,7 +433,7 @@
   <tableColumns count="1">
     <tableColumn id="6" name="edi"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -443,7 +443,7 @@
   <tableColumns count="1">
     <tableColumn id="7" name="inv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -453,17 +453,17 @@
   <tableColumns count="1">
     <tableColumn id="8" name="eph"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_desc_adv" displayName="tbl_desc_adv" ref="I1:I9" headerRowCount="1">
-  <autoFilter ref="I1:I9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_desc_adv" displayName="tbl_desc_adv" ref="I1:I10" headerRowCount="1">
+  <autoFilter ref="I1:I10"/>
   <tableColumns count="1">
     <tableColumn id="9" name="desc_adv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -756,34 +756,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="38" customWidth="1" style="1" min="1" max="1"/>
+    <col width="6" customWidth="1" style="1" min="2" max="2"/>
+    <col width="8" customWidth="1" style="1" min="3" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="14" customWidth="1" style="1" min="6" max="6"/>
+    <col width="20" customWidth="1" style="1" min="7" max="7"/>
+    <col width="22" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="1" min="9" max="9"/>
+    <col width="16" customWidth="1" style="1" min="10" max="10"/>
+    <col width="22" customWidth="1" style="1" min="11" max="11"/>
+    <col width="20" customWidth="1" style="1" min="12" max="12"/>
+    <col width="22" customWidth="1" style="1" min="13" max="13"/>
+    <col width="18" customWidth="1" style="1" min="14" max="14"/>
+    <col width="20" customWidth="1" style="1" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="16" max="18"/>
+    <col width="20" customWidth="1" style="1" min="19" max="19"/>
+    <col width="16" customWidth="1" style="1" min="20" max="20"/>
+    <col width="18" customWidth="1" style="1" min="21" max="21"/>
+    <col width="14" customWidth="1" style="1" min="22" max="22"/>
+    <col width="18" customWidth="1" style="1" min="23" max="23"/>
+    <col width="30" customWidth="1" style="1" min="24" max="24"/>
+    <col width="24" customWidth="1" style="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -904,11 +901,6 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -916,61 +908,61 @@
   </sheetData>
   <dataValidations count="19">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=years</formula1>
+      <formula1>years</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=seasons</formula1>
+      <formula1>seasons</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=categories</formula1>
+      <formula1>categories</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=photographers</formula1>
+      <formula1>photographers</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=directors</formula1>
+      <formula1>directors</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=models</formula1>
+      <formula1>models</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=stylists</formula1>
+      <formula1>stylists</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=hair_list</formula1>
+      <formula1>hair_list</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=makeup_list</formula1>
+      <formula1>makeup_list</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=art_directors</formula1>
+      <formula1>art_directors</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=creative_directors</formula1>
+      <formula1>creative_directors</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=set_designers</formula1>
+      <formula1>set_designers</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=casting_directors</formula1>
+      <formula1>casting_directors</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=production_companies</formula1>
+      <formula1>production_companies</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=agencies</formula1>
+      <formula1>agencies</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=publications</formula1>
+      <formula1>publications</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT($D2)</formula1>
+      <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT("desc_"&amp;$D2)</formula1>
+      <formula1>INDIRECT("desc_"&amp;$D2)</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT(SUBSTITUTE($F2," ","_"))</formula1>
+      <formula1>INDIRECT(SUBSTITUTE($F2," ","_"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -984,7 +976,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AE60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1434,7 +1426,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>aw</t>
+          <t>cruise</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1559,7 +1551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cruise</t>
+          <t>pre-fall</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1674,7 +1666,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pre-fall</t>
+          <t>resort</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1772,11 +1764,6 @@
       <c r="A7" t="n">
         <v>1973</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>resort</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>dazed</t>
@@ -1965,6 +1952,11 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>numero</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>watches</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -2,47 +2,44 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Archive" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="accessories">tbl_accessories[accessories]</definedName>
+    <definedName name="years">tbl_years[years]</definedName>
+    <definedName name="seasons">tbl_seasons[seasons]</definedName>
+    <definedName name="categories">tbl_categories[categories]</definedName>
     <definedName name="adv">tbl_adv[adv]</definedName>
-    <definedName name="agencies">tbl_agencies[agencies]</definedName>
-    <definedName name="art_directors">tbl_art_directors[art_directors]</definedName>
-    <definedName name="casting_directors">tbl_casting_directors[casting_directors]</definedName>
-    <definedName name="categories">tbl_categories[categories]</definedName>
     <definedName name="col">tbl_col[col]</definedName>
-    <definedName name="creative_directors">tbl_creative_directors[creative_directors]</definedName>
-    <definedName name="denim">tbl_denim[denim]</definedName>
+    <definedName name="edi">tbl_edi[edi]</definedName>
+    <definedName name="inv">tbl_inv[inv]</definedName>
+    <definedName name="eph">tbl_eph[eph]</definedName>
     <definedName name="desc_adv">tbl_desc_adv[desc_adv]</definedName>
     <definedName name="desc_col">tbl_desc_col[desc_col]</definedName>
-    <definedName name="directors">tbl_directors[directors]</definedName>
-    <definedName name="edi">tbl_edi[edi]</definedName>
-    <definedName name="eph">tbl_eph[eph]</definedName>
+    <definedName name="jeans">tbl_jeans[jeans]</definedName>
+    <definedName name="underwear">tbl_underwear[underwear]</definedName>
     <definedName name="eyewear">tbl_eyewear[eyewear]</definedName>
     <definedName name="fragrance">tbl_fragrance[fragrance]</definedName>
+    <definedName name="photographers">tbl_photographers[photographers]</definedName>
+    <definedName name="directors">tbl_directors[directors]</definedName>
+    <definedName name="models">tbl_models[models]</definedName>
+    <definedName name="stylists">tbl_stylists[stylists]</definedName>
     <definedName name="hair_list">tbl_hair_list[hair_list]</definedName>
-    <definedName name="inv">tbl_inv[inv]</definedName>
-    <definedName name="jeans">tbl_jeans[jeans]</definedName>
     <definedName name="makeup_list">tbl_makeup_list[makeup_list]</definedName>
-    <definedName name="models">tbl_models[models]</definedName>
-    <definedName name="photographers">tbl_photographers[photographers]</definedName>
+    <definedName name="art_directors">tbl_art_directors[art_directors]</definedName>
+    <definedName name="creative_directors">tbl_creative_directors[creative_directors]</definedName>
+    <definedName name="set_designers">tbl_set_designers[set_designers]</definedName>
+    <definedName name="casting_directors">tbl_casting_directors[casting_directors]</definedName>
     <definedName name="production_companies">tbl_production_companies[production_companies]</definedName>
+    <definedName name="agencies">tbl_agencies[agencies]</definedName>
     <definedName name="publications">tbl_publications[publications]</definedName>
-    <definedName name="rtw">tbl_rtw[rtw]</definedName>
-    <definedName name="seasons">tbl_seasons[seasons]</definedName>
-    <definedName name="set_designers">tbl_set_designers[set_designers]</definedName>
-    <definedName name="shoes">tbl_shoes[shoes]</definedName>
-    <definedName name="stylists">tbl_stylists[stylists]</definedName>
-    <definedName name="underwear">tbl_underwear[underwear]</definedName>
-    <definedName name="years">tbl_years[years]</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -78,12 +75,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -163,7 +159,7 @@
   <tableColumns count="1">
     <tableColumn id="1" name="years"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -173,207 +169,187 @@
   <tableColumns count="1">
     <tableColumn id="10" name="desc_col"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_fragrance" displayName="tbl_fragrance" ref="K1:K13" headerRowCount="1">
-  <autoFilter ref="K1:K13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_jeans" displayName="tbl_jeans" ref="K1:K11" headerRowCount="1">
+  <autoFilter ref="K1:K11"/>
   <tableColumns count="1">
-    <tableColumn id="11" name="fragrance"/>
+    <tableColumn id="11" name="jeans"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_jeans" displayName="tbl_jeans" ref="L1:L5" headerRowCount="1">
-  <autoFilter ref="L1:L5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_underwear" displayName="tbl_underwear" ref="L1:L12" headerRowCount="1">
+  <autoFilter ref="L1:L12"/>
   <tableColumns count="1">
-    <tableColumn id="12" name="jeans"/>
+    <tableColumn id="12" name="underwear"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_underwear" displayName="tbl_underwear" ref="M1:M4" headerRowCount="1">
-  <autoFilter ref="M1:M4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_eyewear" displayName="tbl_eyewear" ref="M1:M2" headerRowCount="1">
+  <autoFilter ref="M1:M2"/>
   <tableColumns count="1">
-    <tableColumn id="13" name="underwear"/>
+    <tableColumn id="13" name="eyewear"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_eyewear" displayName="tbl_eyewear" ref="N1:N2" headerRowCount="1">
-  <autoFilter ref="N1:N2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_fragrance" displayName="tbl_fragrance" ref="N1:N34" headerRowCount="1">
+  <autoFilter ref="N1:N34"/>
   <tableColumns count="1">
-    <tableColumn id="14" name="eyewear"/>
+    <tableColumn id="14" name="fragrance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_denim" displayName="tbl_denim" ref="O1:O2" headerRowCount="1">
-  <autoFilter ref="O1:O2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_photographers" displayName="tbl_photographers" ref="O1:O31" headerRowCount="1">
+  <autoFilter ref="O1:O31"/>
   <tableColumns count="1">
-    <tableColumn id="15" name="denim"/>
+    <tableColumn id="15" name="photographers"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_accessories" displayName="tbl_accessories" ref="P1:P2" headerRowCount="1">
-  <autoFilter ref="P1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_directors" displayName="tbl_directors" ref="P1:P16" headerRowCount="1">
+  <autoFilter ref="P1:P16"/>
   <tableColumns count="1">
-    <tableColumn id="16" name="accessories"/>
+    <tableColumn id="16" name="directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_shoes" displayName="tbl_shoes" ref="Q1:Q2" headerRowCount="1">
-  <autoFilter ref="Q1:Q2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_models" displayName="tbl_models" ref="Q1:Q27" headerRowCount="1">
+  <autoFilter ref="Q1:Q27"/>
   <tableColumns count="1">
-    <tableColumn id="17" name="shoes"/>
+    <tableColumn id="17" name="models"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_rtw" displayName="tbl_rtw" ref="R1:R2" headerRowCount="1">
-  <autoFilter ref="R1:R2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_stylists" displayName="tbl_stylists" ref="R1:R13" headerRowCount="1">
+  <autoFilter ref="R1:R13"/>
   <tableColumns count="1">
-    <tableColumn id="18" name="rtw"/>
+    <tableColumn id="18" name="stylists"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_photographers" displayName="tbl_photographers" ref="S1:S31" headerRowCount="1">
-  <autoFilter ref="S1:S31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_hair_list" displayName="tbl_hair_list" ref="S1:S10" headerRowCount="1">
+  <autoFilter ref="S1:S10"/>
   <tableColumns count="1">
-    <tableColumn id="19" name="photographers"/>
+    <tableColumn id="19" name="hair_list"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_seasons" displayName="tbl_seasons" ref="B1:B7" headerRowCount="1">
-  <autoFilter ref="B1:B7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_seasons" displayName="tbl_seasons" ref="B1:B6" headerRowCount="1">
+  <autoFilter ref="B1:B6"/>
   <tableColumns count="1">
     <tableColumn id="2" name="seasons"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_directors" displayName="tbl_directors" ref="T1:T16" headerRowCount="1">
-  <autoFilter ref="T1:T16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_makeup_list" displayName="tbl_makeup_list" ref="T1:T11" headerRowCount="1">
+  <autoFilter ref="T1:T11"/>
   <tableColumns count="1">
-    <tableColumn id="20" name="directors"/>
+    <tableColumn id="20" name="makeup_list"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_models" displayName="tbl_models" ref="U1:U27" headerRowCount="1">
-  <autoFilter ref="U1:U27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_art_directors" displayName="tbl_art_directors" ref="U1:U6" headerRowCount="1">
+  <autoFilter ref="U1:U6"/>
   <tableColumns count="1">
-    <tableColumn id="21" name="models"/>
+    <tableColumn id="21" name="art_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_stylists" displayName="tbl_stylists" ref="V1:V13" headerRowCount="1">
-  <autoFilter ref="V1:V13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_creative_directors" displayName="tbl_creative_directors" ref="V1:V8" headerRowCount="1">
+  <autoFilter ref="V1:V8"/>
   <tableColumns count="1">
-    <tableColumn id="22" name="stylists"/>
+    <tableColumn id="22" name="creative_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_hair_list" displayName="tbl_hair_list" ref="W1:W10" headerRowCount="1">
-  <autoFilter ref="W1:W10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_set_designers" displayName="tbl_set_designers" ref="W1:W6" headerRowCount="1">
+  <autoFilter ref="W1:W6"/>
   <tableColumns count="1">
-    <tableColumn id="23" name="hair_list"/>
+    <tableColumn id="23" name="set_designers"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_makeup_list" displayName="tbl_makeup_list" ref="X1:X11" headerRowCount="1">
-  <autoFilter ref="X1:X11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_casting_directors" displayName="tbl_casting_directors" ref="X1:X6" headerRowCount="1">
+  <autoFilter ref="X1:X6"/>
   <tableColumns count="1">
-    <tableColumn id="24" name="makeup_list"/>
+    <tableColumn id="24" name="casting_directors"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_art_directors" displayName="tbl_art_directors" ref="Y1:Y6" headerRowCount="1">
-  <autoFilter ref="Y1:Y6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_production_companies" displayName="tbl_production_companies" ref="Y1:Y7" headerRowCount="1">
+  <autoFilter ref="Y1:Y7"/>
   <tableColumns count="1">
-    <tableColumn id="25" name="art_directors"/>
+    <tableColumn id="25" name="production_companies"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_creative_directors" displayName="tbl_creative_directors" ref="Z1:Z8" headerRowCount="1">
-  <autoFilter ref="Z1:Z8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_agencies" displayName="tbl_agencies" ref="Z1:Z7" headerRowCount="1">
+  <autoFilter ref="Z1:Z7"/>
   <tableColumns count="1">
-    <tableColumn id="26" name="creative_directors"/>
+    <tableColumn id="26" name="agencies"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_set_designers" displayName="tbl_set_designers" ref="AA1:AA6" headerRowCount="1">
-  <autoFilter ref="AA1:AA6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_publications" displayName="tbl_publications" ref="AA1:AA17" headerRowCount="1">
+  <autoFilter ref="AA1:AA17"/>
   <tableColumns count="1">
-    <tableColumn id="27" name="set_designers"/>
+    <tableColumn id="27" name="publications"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_casting_directors" displayName="tbl_casting_directors" ref="AB1:AB6" headerRowCount="1">
-  <autoFilter ref="AB1:AB6"/>
-  <tableColumns count="1">
-    <tableColumn id="28" name="casting_directors"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_production_companies" displayName="tbl_production_companies" ref="AC1:AC7" headerRowCount="1">
-  <autoFilter ref="AC1:AC7"/>
-  <tableColumns count="1">
-    <tableColumn id="29" name="production_companies"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -383,27 +359,7 @@
   <tableColumns count="1">
     <tableColumn id="3" name="categories"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_agencies" displayName="tbl_agencies" ref="AD1:AD7" headerRowCount="1">
-  <autoFilter ref="AD1:AD7"/>
-  <tableColumns count="1">
-    <tableColumn id="30" name="agencies"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_publications" displayName="tbl_publications" ref="AE1:AE17" headerRowCount="1">
-  <autoFilter ref="AE1:AE17"/>
-  <tableColumns count="1">
-    <tableColumn id="31" name="publications"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -413,7 +369,7 @@
   <tableColumns count="1">
     <tableColumn id="4" name="adv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -423,7 +379,7 @@
   <tableColumns count="1">
     <tableColumn id="5" name="col"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -433,7 +389,7 @@
   <tableColumns count="1">
     <tableColumn id="6" name="edi"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -443,7 +399,7 @@
   <tableColumns count="1">
     <tableColumn id="7" name="inv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -453,17 +409,17 @@
   <tableColumns count="1">
     <tableColumn id="8" name="eph"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_desc_adv" displayName="tbl_desc_adv" ref="I1:I10" headerRowCount="1">
-  <autoFilter ref="I1:I10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_desc_adv" displayName="tbl_desc_adv" ref="I1:I16" headerRowCount="1">
+  <autoFilter ref="I1:I16"/>
   <tableColumns count="1">
     <tableColumn id="9" name="desc_adv"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -757,30 +713,32 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" style="1" min="1" max="1"/>
-    <col width="6" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8" customWidth="1" style="1" min="3" max="4"/>
-    <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="14" customWidth="1" style="1" min="6" max="6"/>
-    <col width="20" customWidth="1" style="1" min="7" max="7"/>
-    <col width="22" customWidth="1" style="1" min="8" max="8"/>
-    <col width="18" customWidth="1" style="1" min="9" max="9"/>
-    <col width="16" customWidth="1" style="1" min="10" max="10"/>
-    <col width="22" customWidth="1" style="1" min="11" max="11"/>
-    <col width="20" customWidth="1" style="1" min="12" max="12"/>
-    <col width="22" customWidth="1" style="1" min="13" max="13"/>
-    <col width="18" customWidth="1" style="1" min="14" max="14"/>
-    <col width="20" customWidth="1" style="1" min="15" max="15"/>
-    <col width="18" customWidth="1" style="1" min="16" max="18"/>
-    <col width="20" customWidth="1" style="1" min="19" max="19"/>
-    <col width="16" customWidth="1" style="1" min="20" max="20"/>
-    <col width="18" customWidth="1" style="1" min="21" max="21"/>
-    <col width="14" customWidth="1" style="1" min="22" max="22"/>
-    <col width="18" customWidth="1" style="1" min="23" max="23"/>
-    <col width="30" customWidth="1" style="1" min="24" max="24"/>
-    <col width="24" customWidth="1" style="1" min="25" max="25"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -908,61 +866,61 @@
   </sheetData>
   <dataValidations count="19">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>years</formula1>
+      <formula1>=years</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>seasons</formula1>
+      <formula1>=seasons</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>categories</formula1>
+      <formula1>=categories</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>photographers</formula1>
+      <formula1>=photographers</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>directors</formula1>
+      <formula1>=directors</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>models</formula1>
+      <formula1>=models</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>stylists</formula1>
+      <formula1>=stylists</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>hair_list</formula1>
+      <formula1>=hair_list</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>makeup_list</formula1>
+      <formula1>=makeup_list</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>art_directors</formula1>
+      <formula1>=art_directors</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>creative_directors</formula1>
+      <formula1>=creative_directors</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>set_designers</formula1>
+      <formula1>=set_designers</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>casting_directors</formula1>
+      <formula1>=casting_directors</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>production_companies</formula1>
+      <formula1>=production_companies</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>agencies</formula1>
+      <formula1>=agencies</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>publications</formula1>
+      <formula1>=publications</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>INDIRECT($D2)</formula1>
+      <formula1>=INDIRECT($D2)</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>INDIRECT("desc_"&amp;$D2)</formula1>
+      <formula1>=INDIRECT("desc_"&amp;$D2)</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>INDIRECT(SUBSTITUTE($F2," ","_"))</formula1>
+      <formula1>=INDIRECT(SUBSTITUTE($F2," ","_"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -975,8 +933,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:AA60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1031,105 +989,85 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>jeans</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>fragrance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>jeans</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>underwear</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>eyewear</t>
-        </is>
-      </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>denim</t>
+          <t>photographers</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>accessories</t>
+          <t>directors</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>shoes</t>
+          <t>models</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>rtw</t>
+          <t>stylists</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>photographers</t>
+          <t>hair_list</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>directors</t>
+          <t>makeup_list</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>art_directors</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>stylists</t>
+          <t>creative_directors</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>hair_list</t>
+          <t>set_designers</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>makeup_list</t>
+          <t>casting_directors</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>art_directors</t>
+          <t>production_companies</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>creative_directors</t>
+          <t>agencies</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
-        <is>
-          <t>set_designers</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>casting_directors</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>production_companies</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>agencies</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
         <is>
           <t>publications</t>
         </is>
@@ -1176,7 +1114,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1186,105 +1124,85 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>nothing comes between me</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>marky mark underwear</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ck eyewear</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>obsession</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>are you wearing any</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ck underwear</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ck eyewear</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ck denim</t>
+          <t>Bruce Weber</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ck accessories</t>
+          <t>Fabien Baron</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ck shoes</t>
+          <t>Kate Moss</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ck rtw</t>
+          <t>Camilla Nickerson</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Bruce Weber</t>
+          <t>Garren</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>Pat McGrath</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>Fabien Baron</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Kate Moss</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Camilla Nickerson</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Garren</t>
+          <t>Stefan Beckman</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Pat McGrath</t>
+          <t>James Scully</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Fabien Baron</t>
+          <t>Baron &amp; Baron</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Baron &amp; Baron</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
-        <is>
-          <t>Stefan Beckman</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>James Scully</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Baron &amp; Baron</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Baron &amp; Baron</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
@@ -1331,7 +1249,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>jeans</t>
+          <t>ck white</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1341,80 +1259,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>eternity</t>
+          <t>marky mark</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>nothing comes between me</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>my calvins</t>
+          <t>kate moss underwear</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>obsession for men</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Steven Meisel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>David Fincher</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Christy Turlington</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Joe McKenna</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Steven Meisel</t>
+          <t>Guido Palau</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>David Fincher</t>
+          <t>Diane Kendal</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Christy Turlington</t>
+          <t>Sam Shahid</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Joe McKenna</t>
+          <t>Raf Simons</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Guido Palau</t>
+          <t>Mary Howard</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Diane Kendal</t>
+          <t>Piergiorgio Del Moro</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Sam Shahid</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Raf Simons</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
-        <is>
-          <t>Mary Howard</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Piergiorgio Del Moro</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>Vogue Italia</t>
         </is>
@@ -1456,7 +1374,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>underwear</t>
+          <t>jeans</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1466,80 +1384,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ck one</t>
+          <t>kate moss obsession</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>just the way you are</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>i __ my calvins</t>
+          <t>mycalvins</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>eternity</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Richard Avedon</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bruce Weber</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Naomi Campbell</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Karl Templer</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Richard Avedon</t>
+          <t>Sam McKnight</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Bruce Weber</t>
+          <t>Aaron de Mey</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Naomi Campbell</t>
+          <t>Tibor Kalman</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Karl Templer</t>
+          <t>Francisco Costa</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sam McKnight</t>
+          <t>Andy Hillman</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaron de Mey</t>
+          <t>Ashley Brokaw</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Tibor Kalman</t>
+          <t>Calvin Klein Inc.</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Francisco Costa</t>
+          <t>Wieden+Kennedy</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
-        <is>
-          <t>Andy Hillman</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Ashley Brokaw</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Calvin Klein Inc.</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Wieden+Kennedy</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>Vogue Paris</t>
         </is>
@@ -1561,7 +1479,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1581,80 +1499,85 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>eyewear</t>
+          <t>underwear</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>escape</t>
+          <t>heroin chic</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ck jeans</t>
+          <t>justin bieber x lara stone</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>eternity for men</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Herb Ritts</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sofia Coppola</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Cindy Crawford</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Marie-Amélie Sauvé</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Herb Ritts</t>
+          <t>Eugene Souleiman</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Sofia Coppola</t>
+          <t>Tom Pecheux</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Cindy Crawford</t>
+          <t>Neville Brody</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Marie-Amélie Sauvé</t>
+          <t>Italo Zucchelli</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Eugene Souleiman</t>
+          <t>Piers Hanmer</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Tom Pecheux</t>
+          <t>Jess Hallett</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Neville Brody</t>
+          <t>Hungry Man</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Italo Zucchelli</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
-        <is>
-          <t>Piers Hanmer</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Jess Hallett</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hungry Man</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>Harper's Bazaar</t>
         </is>
@@ -1686,75 +1609,85 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>denim</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>contradiction</t>
+          <t>just be</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>kendall jenner</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>escape</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Patrick Demarchelier</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mario Sorrenti</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Linda Evangelista</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Olivier Rizzo</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Patrick Demarchelier</t>
+          <t>Christiaan Houtenbos</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Mario Sorrenti</t>
+          <t>François Nars</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Linda Evangelista</t>
+          <t>Peter Saville</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Olivier Rizzo</t>
+          <t>Kevin Carrigan</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Christiaan Houtenbos</t>
+          <t>Jack Flanagan</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>François Nars</t>
+          <t>Anita Bitton</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Peter Saville</t>
+          <t>RSA Films</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Kevin Carrigan</t>
+          <t>Laird+Partners</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
-        <is>
-          <t>Jack Flanagan</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Anita Bitton</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>RSA Films</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Laird+Partners</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>i-D</t>
         </is>
@@ -1771,60 +1704,70 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>accessories</t>
+          <t>swimwear</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>truth</t>
+          <t>pro wash</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i __ in mycalvins</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>escape for men</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mario Sorrenti</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Steven Meisel</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Brooke Shields</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Alastair McKimm</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Mario Sorrenti</t>
+          <t>Didier Malige</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Steven Meisel</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Brooke Shields</t>
+          <t>Kevyn Aucoin</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Alastair McKimm</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Didier Malige</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Kevyn Aucoin</t>
+          <t>Pieter Mulier</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Anonymous Content</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Pieter Mulier</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Anonymous Content</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
           <t>CKX</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Dazed</t>
         </is>
@@ -1841,50 +1784,60 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shoes</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>mycalvins</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>our now</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ck one</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>David Sims</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Herb Ritts</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Mark Wahlberg</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Lucinda Chambers</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>David Sims</t>
+          <t>Julien d'Ys</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Herb Ritts</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Mark Wahlberg</t>
+          <t>Linda Cantello</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Lucinda Chambers</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Julien d'Ys</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Linda Cantello</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
           <t>Veronica Leoni</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Interview</t>
         </is>
@@ -1901,45 +1854,55 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rtw</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>euphoria</t>
+          <t>justin bieber</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>calvins or nothing</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ck be</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mert &amp; Marcus</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spike Jonze</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Travis Fimmel</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Carlyne Cerf de Dudzeele</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Mert &amp; Marcus</t>
+          <t>Anthony Turner</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Spike Jonze</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Travis Fimmel</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Carlyne Cerf de Dudzeele</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Anthony Turner</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
           <t>Charlotte Tilbury</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>W Magazine</t>
         </is>
@@ -1956,45 +1919,55 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>watches</t>
+          <t>footwear</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ck2</t>
+          <t>or nothing</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>jeremy allen white</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>contradiction</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Steven Klein</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tony Kaye</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Lara Stone</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Grace Coddington</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Steven Klein</t>
+          <t>Duffy</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Tony Kaye</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Lara Stone</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Grace Coddington</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Duffy</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
           <t>Lucia Pieroni</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Numéro</t>
         </is>
@@ -2009,37 +1982,52 @@
           <t>theface</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>eternity moment</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+          <t>i love my calvins</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>fka twigs or nothing</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>truth</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Inez &amp; Vinoodh</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jonas Åkerlund</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Natalia Vodianova</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Carine Roitfeld</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Jonas Åkerlund</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Natalia Vodianova</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Carine Roitfeld</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
           <t>Peter Philips</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Self Service</t>
         </is>
@@ -2049,32 +2037,42 @@
       <c r="A12" t="n">
         <v>1978</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>watches jewelry</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>greta lee</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>crave</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Mario Testino</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Mark Romanek</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Jamie Dornan</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Melanie Ward</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
@@ -2084,32 +2082,37 @@
       <c r="A13" t="n">
         <v>1979</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ck all</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fragrance</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>euphoria</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Glen Luchford</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Floria Sigismondi</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Gisele Bündchen</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Tonne Goodman</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Another</t>
         </is>
@@ -2119,22 +2122,32 @@
       <c r="A14" t="n">
         <v>1980</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>euphoria for men</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Craig McDean</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Steven Klein</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Jessica Stam</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>The Face</t>
         </is>
@@ -2144,22 +2157,32 @@
       <c r="A15" t="n">
         <v>1981</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>platinum</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ck in2u</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Willy Vanderperre</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Mert &amp; Marcus</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Daria Werbowy</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AnOther Man</t>
         </is>
@@ -2169,22 +2192,32 @@
       <c r="A16" t="n">
         <v>1982</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>secret obsession</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Fabien Baron</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sam Taylor-Johnson</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Edie Campbell</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>GQ</t>
         </is>
@@ -2194,17 +2227,22 @@
       <c r="A17" t="n">
         <v>1983</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>beauty</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Peter Lindbergh</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Anna Ewers</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Vanity Fair</t>
         </is>
@@ -2214,12 +2252,17 @@
       <c r="A18" t="n">
         <v>1984</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>forbidden euphoria</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Helmut Newton</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Saskia de Brauw</t>
         </is>
@@ -2229,12 +2272,17 @@
       <c r="A19" t="n">
         <v>1985</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>encounter</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Annie Leibovitz</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Justin Bieber</t>
         </is>
@@ -2244,12 +2292,17 @@
       <c r="A20" t="n">
         <v>1986</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>downtown</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Nick Knight</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Kendall Jenner</t>
         </is>
@@ -2259,12 +2312,17 @@
       <c r="A21" t="n">
         <v>1987</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>reveal</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Juergen Teller</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Bella Hadid</t>
         </is>
@@ -2274,12 +2332,17 @@
       <c r="A22" t="n">
         <v>1988</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>endless euphoria</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Tyrone Lebon</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Lily-Rose Depp</t>
         </is>
@@ -2289,12 +2352,17 @@
       <c r="A23" t="n">
         <v>1989</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>eternity now</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Lachlan Bailey</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>FKA twigs</t>
         </is>
@@ -2304,12 +2372,17 @@
       <c r="A24" t="n">
         <v>1990</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>deep euphoria</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Cass Bird</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Solange</t>
         </is>
@@ -2319,12 +2392,17 @@
       <c r="A25" t="n">
         <v>1991</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>ck2</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Harley Weir</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>A$AP Rocky</t>
         </is>
@@ -2334,12 +2412,17 @@
       <c r="A26" t="n">
         <v>1992</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ck one gold</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>Daniel Jackson</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Kaia Gerber</t>
         </is>
@@ -2349,12 +2432,17 @@
       <c r="A27" t="n">
         <v>1993</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>obsessed</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Niall McInerney</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Jeremy Allen White</t>
         </is>
@@ -2364,7 +2452,12 @@
       <c r="A28" t="n">
         <v>1994</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sølve Sundsbø</t>
         </is>
@@ -2374,7 +2467,12 @@
       <c r="A29" t="n">
         <v>1995</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>eternity air</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>Paolo Roversi</t>
         </is>
@@ -2384,7 +2482,12 @@
       <c r="A30" t="n">
         <v>1996</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>defy</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Collier Schorr</t>
         </is>
@@ -2394,7 +2497,12 @@
       <c r="A31" t="n">
         <v>1997</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ck everyone</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Ethan James Green</t>
         </is>
@@ -2404,16 +2512,31 @@
       <c r="A32" t="n">
         <v>1998</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ck free</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>1999</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ck all</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2000</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>eternity moment</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2547,7 +2670,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="31">
+  <tableParts count="27">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
@@ -2575,10 +2698,6 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -1731,7 +1731,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1985_adv_print_hosier_001</t>
+          <t>1985_adv_print_hosiery_001</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>hosier</t>
+          <t>hosiery</t>
         </is>
       </c>
     </row>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -7046,7 +7046,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1999_ss_adv_print_collection_004</t>
+          <t>1999_ss_adv_print_collection_menswear_001</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -7072,11 +7072,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>menswear</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1999_ss_adv_print_collection_005</t>
+          <t>1999_ss_adv_print_collection_menswear_002</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -7102,11 +7107,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>menswear</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1999_ss_adv_print_collection_menswear_001</t>
+          <t>1999_ss_adv_print_eyewear_001</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -7129,19 +7139,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>menswear</t>
+          <t>eyewear</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1999_ss_adv_print_collection_menswear_002</t>
+          <t>1999_ss_adv_print_eyewear_002</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -7164,19 +7169,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>menswear</t>
+          <t>eyewear</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1999_ss_adv_print_eyewear_001</t>
+          <t>1999_ss_adv_print_eyewear_003</t>
         </is>
       </c>
       <c r="B206" t="n">

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -3931,7 +3931,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1995_ss_adv_print_fragrance_obsession_men_001</t>
+          <t>1995_ss_adv_print_fragrance_obsession_formen_001</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>obsession_men</t>
+          <t>obsession_formen</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1997_ss_adv_print_fragrance_obsession_men_001</t>
+          <t>1997_ss_adv_print_fragrance_obsession_formen_001</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>obsession_men</t>
+          <t>obsession_formen</t>
         </is>
       </c>
     </row>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X297"/>
+  <dimension ref="A1:X320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,7 +549,6 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>adv</t>
@@ -565,24 +564,6 @@
           <t>fragrance</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -595,7 +576,6 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>adv</t>
@@ -611,24 +591,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -641,7 +603,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>adv</t>
@@ -657,24 +618,6 @@
           <t>belts</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -687,7 +630,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>adv</t>
@@ -703,24 +645,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -733,7 +657,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>adv</t>
@@ -749,24 +672,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -779,7 +684,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>adv</t>
@@ -795,24 +699,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -825,7 +711,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>adv</t>
@@ -841,24 +726,6 @@
           <t>cosmetics</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -871,7 +738,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>adv</t>
@@ -887,24 +753,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,7 +765,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>adv</t>
@@ -933,24 +780,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -963,7 +792,6 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>adv</t>
@@ -979,24 +807,6 @@
           <t>scarves</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1029,24 +839,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1059,7 +851,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1075,24 +866,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1105,7 +878,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1121,24 +893,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1151,7 +905,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1167,24 +920,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1197,7 +932,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1213,24 +947,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1243,7 +959,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1259,24 +974,6 @@
           <t>fragrance</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1289,7 +986,6 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1305,24 +1001,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1335,7 +1013,6 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1351,24 +1028,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1381,7 +1040,6 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1397,24 +1055,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1427,7 +1067,6 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1443,24 +1082,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1473,7 +1094,6 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1489,24 +1109,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1519,7 +1121,6 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1535,24 +1136,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1565,7 +1148,6 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1581,24 +1163,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1611,7 +1175,6 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1627,24 +1190,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1657,7 +1202,6 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1678,23 +1222,6 @@
           <t>boyswear</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1707,7 +1234,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1723,24 +1249,6 @@
           <t>beauty</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1753,7 +1261,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1769,24 +1276,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1799,7 +1288,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1815,24 +1303,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1845,7 +1315,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1861,24 +1330,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1891,7 +1342,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1907,24 +1357,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1937,7 +1369,6 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1953,24 +1384,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1983,7 +1396,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>adv</t>
@@ -1999,24 +1411,6 @@
           <t>footwear</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2029,7 +1423,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2045,24 +1438,6 @@
           <t>fragrance</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2075,7 +1450,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2096,23 +1470,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2125,7 +1482,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2141,24 +1497,6 @@
           <t>hosiery</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2171,7 +1509,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2187,24 +1524,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2217,7 +1536,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2233,24 +1551,6 @@
           <t>sport</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2263,7 +1563,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2279,24 +1578,6 @@
           <t>sport</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2309,7 +1590,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2325,24 +1605,6 @@
           <t>sport</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2375,24 +1637,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2425,24 +1669,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2475,24 +1701,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2525,24 +1733,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2575,24 +1765,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2605,7 +1777,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2621,24 +1792,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2651,7 +1804,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2672,23 +1824,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2701,7 +1836,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2722,23 +1856,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2751,7 +1868,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2767,24 +1883,6 @@
           <t>furs</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2797,7 +1895,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2813,24 +1910,6 @@
           <t>hosiery</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2843,7 +1922,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2859,24 +1937,6 @@
           <t>sport</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2889,7 +1949,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2905,24 +1964,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2935,7 +1976,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2951,24 +1991,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2981,7 +2003,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>adv</t>
@@ -2997,24 +2018,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3027,7 +2030,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>adv</t>
@@ -3043,24 +2045,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3093,24 +2077,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3143,24 +2109,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3193,24 +2141,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3243,24 +2173,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3293,24 +2205,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3343,24 +2237,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3393,24 +2269,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3443,24 +2301,6 @@
           <t>footwear</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3493,24 +2333,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3543,24 +2365,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3593,24 +2397,6 @@
           <t>classifications</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3643,24 +2429,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3693,24 +2461,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3743,24 +2493,6 @@
           <t>footwear</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3793,24 +2525,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3848,23 +2562,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3902,23 +2599,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3951,24 +2631,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4006,23 +2668,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4060,23 +2705,6 @@
           <t>escape_men</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4114,23 +2742,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4168,23 +2779,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4217,24 +2811,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4267,24 +2843,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4322,23 +2880,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4371,24 +2912,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4426,23 +2949,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4480,23 +2986,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4534,23 +3023,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4583,24 +3055,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4638,23 +3092,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4692,23 +3129,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4746,23 +3166,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4800,23 +3203,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4849,24 +3235,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4899,24 +3267,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4949,24 +3299,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4999,24 +3331,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5054,23 +3368,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5103,24 +3400,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5158,23 +3437,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5212,23 +3474,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5261,24 +3506,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5311,24 +3538,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5361,24 +3570,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5411,24 +3602,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5461,24 +3634,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5511,24 +3666,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5566,23 +3703,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5620,23 +3740,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5674,23 +3777,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5728,23 +3814,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5782,23 +3851,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5831,24 +3883,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5881,24 +3915,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5931,24 +3947,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5981,24 +3979,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6036,23 +4016,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6090,23 +4053,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6144,23 +4090,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6198,23 +4127,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6252,23 +4164,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6306,23 +4201,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6360,23 +4238,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6414,23 +4275,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6468,23 +4312,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6522,23 +4349,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6576,23 +4386,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6630,23 +4423,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6684,23 +4460,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6738,23 +4497,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6792,23 +4534,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6846,23 +4571,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6895,24 +4603,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6945,24 +4635,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6995,24 +4667,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7050,23 +4704,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7104,23 +4741,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7158,23 +4778,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7212,23 +4815,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7266,23 +4852,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7320,23 +4889,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7369,24 +4921,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7419,24 +4953,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7474,23 +4990,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7528,23 +5027,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7582,23 +5064,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7636,23 +5101,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7690,23 +5138,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7739,24 +5170,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7789,24 +5202,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7839,24 +5234,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7889,24 +5266,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7939,24 +5298,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7989,24 +5330,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8044,23 +5367,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8098,23 +5404,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8152,23 +5441,6 @@
           <t>escape_men</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8206,23 +5478,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8260,23 +5515,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
-      <c r="X155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8309,24 +5547,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
-      <c r="X156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8364,23 +5584,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
-      <c r="X157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8418,23 +5621,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
-      <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
-      <c r="X158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8472,23 +5658,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
-      <c r="X159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8526,23 +5695,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
-      <c r="X160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8575,24 +5727,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
-      <c r="X161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8630,23 +5764,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
-      <c r="X162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8684,23 +5801,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
-      <c r="X163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8738,23 +5838,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
-      <c r="X164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8787,24 +5870,6 @@
           <t>swimwear</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
-      <c r="X165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8837,24 +5902,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr"/>
-      <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
-      <c r="X166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8887,24 +5934,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
-      <c r="X167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8937,24 +5966,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8987,24 +5998,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9037,24 +6030,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9087,24 +6062,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9142,23 +6099,6 @@
           <t>ck</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
-      <c r="X172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9196,23 +6136,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
-      <c r="X173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9245,24 +6168,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
-      <c r="X174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9295,24 +6200,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
-      <c r="X175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9350,23 +6237,6 @@
           <t>be</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
-      <c r="X176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9404,23 +6274,6 @@
           <t>contradiction</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
-      <c r="X177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9458,23 +6311,6 @@
           <t>contradiction</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
-      <c r="X178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9512,23 +6348,6 @@
           <t>contradiction_men</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
-      <c r="X179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9566,23 +6385,6 @@
           <t>contradiction_men</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
-      <c r="X180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9620,23 +6422,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
-      <c r="X181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9674,23 +6459,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
-      <c r="X182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9728,23 +6496,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
-      <c r="W183" t="inlineStr"/>
-      <c r="X183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9777,24 +6528,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr"/>
-      <c r="X184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9827,24 +6560,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
-      <c r="X185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9877,24 +6592,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
-      <c r="W186" t="inlineStr"/>
-      <c r="X186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9927,24 +6624,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9982,23 +6661,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
-      <c r="W188" t="inlineStr"/>
-      <c r="X188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10036,23 +6698,6 @@
           <t>eternity_men</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10090,23 +6735,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
-      <c r="X190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10144,23 +6772,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
-      <c r="X191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10198,23 +6809,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10247,24 +6841,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
-      <c r="W193" t="inlineStr"/>
-      <c r="X193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10302,23 +6878,6 @@
           <t>contradiction_men</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
-      <c r="X194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10356,23 +6915,6 @@
           <t>contradiction_men</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
-      <c r="X195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10410,23 +6952,6 @@
           <t>contradiction_men</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
-      <c r="X196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10464,23 +6989,6 @@
           <t>escape</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
-      <c r="X197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10513,24 +7021,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
-      <c r="X198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10563,24 +7053,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr"/>
-      <c r="X199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10613,24 +7085,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
-      <c r="X200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10663,24 +7117,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr"/>
-      <c r="X201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10718,23 +7154,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10772,23 +7191,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr"/>
-      <c r="X203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10821,24 +7223,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
-      <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr"/>
-      <c r="W204" t="inlineStr"/>
-      <c r="X204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10871,24 +7255,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
-      <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr"/>
-      <c r="X205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10921,24 +7287,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr"/>
-      <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr"/>
-      <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10976,23 +7324,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr"/>
-      <c r="U207" t="inlineStr"/>
-      <c r="V207" t="inlineStr"/>
-      <c r="W207" t="inlineStr"/>
-      <c r="X207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11030,23 +7361,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr"/>
-      <c r="U208" t="inlineStr"/>
-      <c r="V208" t="inlineStr"/>
-      <c r="W208" t="inlineStr"/>
-      <c r="X208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11084,23 +7398,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
-      <c r="W209" t="inlineStr"/>
-      <c r="X209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11138,23 +7435,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
-      <c r="U210" t="inlineStr"/>
-      <c r="V210" t="inlineStr"/>
-      <c r="W210" t="inlineStr"/>
-      <c r="X210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11192,23 +7472,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr"/>
-      <c r="U211" t="inlineStr"/>
-      <c r="V211" t="inlineStr"/>
-      <c r="W211" t="inlineStr"/>
-      <c r="X211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11246,23 +7509,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
-      <c r="T212" t="inlineStr"/>
-      <c r="U212" t="inlineStr"/>
-      <c r="V212" t="inlineStr"/>
-      <c r="W212" t="inlineStr"/>
-      <c r="X212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11300,23 +7546,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
-      <c r="T213" t="inlineStr"/>
-      <c r="U213" t="inlineStr"/>
-      <c r="V213" t="inlineStr"/>
-      <c r="W213" t="inlineStr"/>
-      <c r="X213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11354,23 +7583,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr"/>
-      <c r="U214" t="inlineStr"/>
-      <c r="V214" t="inlineStr"/>
-      <c r="W214" t="inlineStr"/>
-      <c r="X214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11408,23 +7620,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
-      <c r="T215" t="inlineStr"/>
-      <c r="U215" t="inlineStr"/>
-      <c r="V215" t="inlineStr"/>
-      <c r="W215" t="inlineStr"/>
-      <c r="X215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11457,24 +7652,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
-      <c r="T216" t="inlineStr"/>
-      <c r="U216" t="inlineStr"/>
-      <c r="V216" t="inlineStr"/>
-      <c r="W216" t="inlineStr"/>
-      <c r="X216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11507,24 +7684,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
-      <c r="W217" t="inlineStr"/>
-      <c r="X217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11557,24 +7716,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
-      <c r="U218" t="inlineStr"/>
-      <c r="V218" t="inlineStr"/>
-      <c r="W218" t="inlineStr"/>
-      <c r="X218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11612,23 +7753,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
-      <c r="V219" t="inlineStr"/>
-      <c r="W219" t="inlineStr"/>
-      <c r="X219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11666,23 +7790,6 @@
           <t>truth</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
-      <c r="T220" t="inlineStr"/>
-      <c r="U220" t="inlineStr"/>
-      <c r="V220" t="inlineStr"/>
-      <c r="W220" t="inlineStr"/>
-      <c r="X220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11720,23 +7827,6 @@
           <t>truth</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
-      <c r="U221" t="inlineStr"/>
-      <c r="V221" t="inlineStr"/>
-      <c r="W221" t="inlineStr"/>
-      <c r="X221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11769,24 +7859,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
-      <c r="W222" t="inlineStr"/>
-      <c r="X222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11819,24 +7891,6 @@
           <t>beauty</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
-      <c r="V223" t="inlineStr"/>
-      <c r="W223" t="inlineStr"/>
-      <c r="X223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11869,24 +7923,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
-      <c r="U224" t="inlineStr"/>
-      <c r="V224" t="inlineStr"/>
-      <c r="W224" t="inlineStr"/>
-      <c r="X224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11919,24 +7955,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
-      <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
-      <c r="W225" t="inlineStr"/>
-      <c r="X225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11969,24 +7987,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
-      <c r="T226" t="inlineStr"/>
-      <c r="U226" t="inlineStr"/>
-      <c r="V226" t="inlineStr"/>
-      <c r="W226" t="inlineStr"/>
-      <c r="X226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12019,24 +8019,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
-      <c r="T227" t="inlineStr"/>
-      <c r="U227" t="inlineStr"/>
-      <c r="V227" t="inlineStr"/>
-      <c r="W227" t="inlineStr"/>
-      <c r="X227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12069,24 +8051,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
-      <c r="W228" t="inlineStr"/>
-      <c r="X228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12119,24 +8083,6 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
-      <c r="T229" t="inlineStr"/>
-      <c r="U229" t="inlineStr"/>
-      <c r="V229" t="inlineStr"/>
-      <c r="W229" t="inlineStr"/>
-      <c r="X229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12169,24 +8115,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
-      <c r="T230" t="inlineStr"/>
-      <c r="U230" t="inlineStr"/>
-      <c r="V230" t="inlineStr"/>
-      <c r="W230" t="inlineStr"/>
-      <c r="X230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12224,23 +8152,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr"/>
-      <c r="W231" t="inlineStr"/>
-      <c r="X231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12278,23 +8189,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
-      <c r="T232" t="inlineStr"/>
-      <c r="U232" t="inlineStr"/>
-      <c r="V232" t="inlineStr"/>
-      <c r="W232" t="inlineStr"/>
-      <c r="X232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12332,23 +8226,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
-      <c r="T233" t="inlineStr"/>
-      <c r="U233" t="inlineStr"/>
-      <c r="V233" t="inlineStr"/>
-      <c r="W233" t="inlineStr"/>
-      <c r="X233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12386,23 +8263,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr"/>
-      <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
-      <c r="W234" t="inlineStr"/>
-      <c r="X234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12435,24 +8295,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
-      <c r="T235" t="inlineStr"/>
-      <c r="U235" t="inlineStr"/>
-      <c r="V235" t="inlineStr"/>
-      <c r="W235" t="inlineStr"/>
-      <c r="X235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12485,24 +8327,6 @@
           <t>beauty</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
-      <c r="T236" t="inlineStr"/>
-      <c r="U236" t="inlineStr"/>
-      <c r="V236" t="inlineStr"/>
-      <c r="W236" t="inlineStr"/>
-      <c r="X236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12535,24 +8359,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr"/>
-      <c r="S237" t="inlineStr"/>
-      <c r="T237" t="inlineStr"/>
-      <c r="U237" t="inlineStr"/>
-      <c r="V237" t="inlineStr"/>
-      <c r="W237" t="inlineStr"/>
-      <c r="X237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12585,24 +8391,6 @@
           <t>eyewear</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
-      <c r="S238" t="inlineStr"/>
-      <c r="T238" t="inlineStr"/>
-      <c r="U238" t="inlineStr"/>
-      <c r="V238" t="inlineStr"/>
-      <c r="W238" t="inlineStr"/>
-      <c r="X238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12635,24 +8423,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
-      <c r="S239" t="inlineStr"/>
-      <c r="T239" t="inlineStr"/>
-      <c r="U239" t="inlineStr"/>
-      <c r="V239" t="inlineStr"/>
-      <c r="W239" t="inlineStr"/>
-      <c r="X239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12690,23 +8460,6 @@
           <t>crave</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
-      <c r="S240" t="inlineStr"/>
-      <c r="T240" t="inlineStr"/>
-      <c r="U240" t="inlineStr"/>
-      <c r="V240" t="inlineStr"/>
-      <c r="W240" t="inlineStr"/>
-      <c r="X240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12744,23 +8497,6 @@
           <t>truth_men</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
-      <c r="T241" t="inlineStr"/>
-      <c r="U241" t="inlineStr"/>
-      <c r="V241" t="inlineStr"/>
-      <c r="W241" t="inlineStr"/>
-      <c r="X241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12793,24 +8529,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
-      <c r="T242" t="inlineStr"/>
-      <c r="U242" t="inlineStr"/>
-      <c r="V242" t="inlineStr"/>
-      <c r="W242" t="inlineStr"/>
-      <c r="X242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12843,24 +8561,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr"/>
-      <c r="U243" t="inlineStr"/>
-      <c r="V243" t="inlineStr"/>
-      <c r="W243" t="inlineStr"/>
-      <c r="X243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12893,24 +8593,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
-      <c r="T244" t="inlineStr"/>
-      <c r="U244" t="inlineStr"/>
-      <c r="V244" t="inlineStr"/>
-      <c r="W244" t="inlineStr"/>
-      <c r="X244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12943,24 +8625,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
-      <c r="T245" t="inlineStr"/>
-      <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
-      <c r="W245" t="inlineStr"/>
-      <c r="X245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12993,24 +8657,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
-      <c r="R246" t="inlineStr"/>
-      <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr"/>
-      <c r="U246" t="inlineStr"/>
-      <c r="V246" t="inlineStr"/>
-      <c r="W246" t="inlineStr"/>
-      <c r="X246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13043,24 +8689,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
-      <c r="R247" t="inlineStr"/>
-      <c r="S247" t="inlineStr"/>
-      <c r="T247" t="inlineStr"/>
-      <c r="U247" t="inlineStr"/>
-      <c r="V247" t="inlineStr"/>
-      <c r="W247" t="inlineStr"/>
-      <c r="X247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13093,24 +8721,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
-      <c r="R248" t="inlineStr"/>
-      <c r="S248" t="inlineStr"/>
-      <c r="T248" t="inlineStr"/>
-      <c r="U248" t="inlineStr"/>
-      <c r="V248" t="inlineStr"/>
-      <c r="W248" t="inlineStr"/>
-      <c r="X248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13143,24 +8753,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
-      <c r="R249" t="inlineStr"/>
-      <c r="S249" t="inlineStr"/>
-      <c r="T249" t="inlineStr"/>
-      <c r="U249" t="inlineStr"/>
-      <c r="V249" t="inlineStr"/>
-      <c r="W249" t="inlineStr"/>
-      <c r="X249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13193,24 +8785,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr"/>
-      <c r="R250" t="inlineStr"/>
-      <c r="S250" t="inlineStr"/>
-      <c r="T250" t="inlineStr"/>
-      <c r="U250" t="inlineStr"/>
-      <c r="V250" t="inlineStr"/>
-      <c r="W250" t="inlineStr"/>
-      <c r="X250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13243,24 +8817,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
-      <c r="S251" t="inlineStr"/>
-      <c r="T251" t="inlineStr"/>
-      <c r="U251" t="inlineStr"/>
-      <c r="V251" t="inlineStr"/>
-      <c r="W251" t="inlineStr"/>
-      <c r="X251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13293,24 +8849,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr"/>
-      <c r="R252" t="inlineStr"/>
-      <c r="S252" t="inlineStr"/>
-      <c r="T252" t="inlineStr"/>
-      <c r="U252" t="inlineStr"/>
-      <c r="V252" t="inlineStr"/>
-      <c r="W252" t="inlineStr"/>
-      <c r="X252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13348,23 +8886,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="inlineStr"/>
-      <c r="S253" t="inlineStr"/>
-      <c r="T253" t="inlineStr"/>
-      <c r="U253" t="inlineStr"/>
-      <c r="V253" t="inlineStr"/>
-      <c r="W253" t="inlineStr"/>
-      <c r="X253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13402,23 +8923,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
-      <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="inlineStr"/>
-      <c r="R254" t="inlineStr"/>
-      <c r="S254" t="inlineStr"/>
-      <c r="T254" t="inlineStr"/>
-      <c r="U254" t="inlineStr"/>
-      <c r="V254" t="inlineStr"/>
-      <c r="W254" t="inlineStr"/>
-      <c r="X254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13456,23 +8960,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
-      <c r="R255" t="inlineStr"/>
-      <c r="S255" t="inlineStr"/>
-      <c r="T255" t="inlineStr"/>
-      <c r="U255" t="inlineStr"/>
-      <c r="V255" t="inlineStr"/>
-      <c r="W255" t="inlineStr"/>
-      <c r="X255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13510,23 +8997,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
-      <c r="R256" t="inlineStr"/>
-      <c r="S256" t="inlineStr"/>
-      <c r="T256" t="inlineStr"/>
-      <c r="U256" t="inlineStr"/>
-      <c r="V256" t="inlineStr"/>
-      <c r="W256" t="inlineStr"/>
-      <c r="X256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13564,23 +9034,6 @@
           <t>truth</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr"/>
-      <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="inlineStr"/>
-      <c r="R257" t="inlineStr"/>
-      <c r="S257" t="inlineStr"/>
-      <c r="T257" t="inlineStr"/>
-      <c r="U257" t="inlineStr"/>
-      <c r="V257" t="inlineStr"/>
-      <c r="W257" t="inlineStr"/>
-      <c r="X257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13613,24 +9066,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
-      <c r="R258" t="inlineStr"/>
-      <c r="S258" t="inlineStr"/>
-      <c r="T258" t="inlineStr"/>
-      <c r="U258" t="inlineStr"/>
-      <c r="V258" t="inlineStr"/>
-      <c r="W258" t="inlineStr"/>
-      <c r="X258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13663,24 +9098,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
-      <c r="R259" t="inlineStr"/>
-      <c r="S259" t="inlineStr"/>
-      <c r="T259" t="inlineStr"/>
-      <c r="U259" t="inlineStr"/>
-      <c r="V259" t="inlineStr"/>
-      <c r="W259" t="inlineStr"/>
-      <c r="X259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13713,24 +9130,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
-      <c r="R260" t="inlineStr"/>
-      <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr"/>
-      <c r="U260" t="inlineStr"/>
-      <c r="V260" t="inlineStr"/>
-      <c r="W260" t="inlineStr"/>
-      <c r="X260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13763,24 +9162,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr"/>
-      <c r="S261" t="inlineStr"/>
-      <c r="T261" t="inlineStr"/>
-      <c r="U261" t="inlineStr"/>
-      <c r="V261" t="inlineStr"/>
-      <c r="W261" t="inlineStr"/>
-      <c r="X261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13813,24 +9194,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr"/>
-      <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr"/>
-      <c r="R262" t="inlineStr"/>
-      <c r="S262" t="inlineStr"/>
-      <c r="T262" t="inlineStr"/>
-      <c r="U262" t="inlineStr"/>
-      <c r="V262" t="inlineStr"/>
-      <c r="W262" t="inlineStr"/>
-      <c r="X262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13863,24 +9226,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
-      <c r="R263" t="inlineStr"/>
-      <c r="S263" t="inlineStr"/>
-      <c r="T263" t="inlineStr"/>
-      <c r="U263" t="inlineStr"/>
-      <c r="V263" t="inlineStr"/>
-      <c r="W263" t="inlineStr"/>
-      <c r="X263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13918,23 +9263,6 @@
           <t>menswear</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
-      <c r="R264" t="inlineStr"/>
-      <c r="S264" t="inlineStr"/>
-      <c r="T264" t="inlineStr"/>
-      <c r="U264" t="inlineStr"/>
-      <c r="V264" t="inlineStr"/>
-      <c r="W264" t="inlineStr"/>
-      <c r="X264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13967,24 +9295,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="inlineStr"/>
-      <c r="S265" t="inlineStr"/>
-      <c r="T265" t="inlineStr"/>
-      <c r="U265" t="inlineStr"/>
-      <c r="V265" t="inlineStr"/>
-      <c r="W265" t="inlineStr"/>
-      <c r="X265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14017,24 +9327,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
-      <c r="R266" t="inlineStr"/>
-      <c r="S266" t="inlineStr"/>
-      <c r="T266" t="inlineStr"/>
-      <c r="U266" t="inlineStr"/>
-      <c r="V266" t="inlineStr"/>
-      <c r="W266" t="inlineStr"/>
-      <c r="X266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14067,24 +9359,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
-      <c r="R267" t="inlineStr"/>
-      <c r="S267" t="inlineStr"/>
-      <c r="T267" t="inlineStr"/>
-      <c r="U267" t="inlineStr"/>
-      <c r="V267" t="inlineStr"/>
-      <c r="W267" t="inlineStr"/>
-      <c r="X267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14117,24 +9391,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
-      <c r="R268" t="inlineStr"/>
-      <c r="S268" t="inlineStr"/>
-      <c r="T268" t="inlineStr"/>
-      <c r="U268" t="inlineStr"/>
-      <c r="V268" t="inlineStr"/>
-      <c r="W268" t="inlineStr"/>
-      <c r="X268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14167,24 +9423,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
-      <c r="R269" t="inlineStr"/>
-      <c r="S269" t="inlineStr"/>
-      <c r="T269" t="inlineStr"/>
-      <c r="U269" t="inlineStr"/>
-      <c r="V269" t="inlineStr"/>
-      <c r="W269" t="inlineStr"/>
-      <c r="X269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14217,24 +9455,6 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
-      <c r="R270" t="inlineStr"/>
-      <c r="S270" t="inlineStr"/>
-      <c r="T270" t="inlineStr"/>
-      <c r="U270" t="inlineStr"/>
-      <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
-      <c r="X270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14267,24 +9487,6 @@
           <t>underwear</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
-      <c r="R271" t="inlineStr"/>
-      <c r="S271" t="inlineStr"/>
-      <c r="T271" t="inlineStr"/>
-      <c r="U271" t="inlineStr"/>
-      <c r="V271" t="inlineStr"/>
-      <c r="W271" t="inlineStr"/>
-      <c r="X271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14317,24 +9519,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
-      <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
-      <c r="R272" t="inlineStr"/>
-      <c r="S272" t="inlineStr"/>
-      <c r="T272" t="inlineStr"/>
-      <c r="U272" t="inlineStr"/>
-      <c r="V272" t="inlineStr"/>
-      <c r="W272" t="inlineStr"/>
-      <c r="X272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14367,24 +9551,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
-      <c r="O273" t="inlineStr"/>
-      <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
-      <c r="R273" t="inlineStr"/>
-      <c r="S273" t="inlineStr"/>
-      <c r="T273" t="inlineStr"/>
-      <c r="U273" t="inlineStr"/>
-      <c r="V273" t="inlineStr"/>
-      <c r="W273" t="inlineStr"/>
-      <c r="X273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14417,24 +9583,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
-      <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="inlineStr"/>
-      <c r="R274" t="inlineStr"/>
-      <c r="S274" t="inlineStr"/>
-      <c r="T274" t="inlineStr"/>
-      <c r="U274" t="inlineStr"/>
-      <c r="V274" t="inlineStr"/>
-      <c r="W274" t="inlineStr"/>
-      <c r="X274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14467,24 +9615,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
-      <c r="O275" t="inlineStr"/>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
-      <c r="R275" t="inlineStr"/>
-      <c r="S275" t="inlineStr"/>
-      <c r="T275" t="inlineStr"/>
-      <c r="U275" t="inlineStr"/>
-      <c r="V275" t="inlineStr"/>
-      <c r="W275" t="inlineStr"/>
-      <c r="X275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14517,24 +9647,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
-      <c r="R276" t="inlineStr"/>
-      <c r="S276" t="inlineStr"/>
-      <c r="T276" t="inlineStr"/>
-      <c r="U276" t="inlineStr"/>
-      <c r="V276" t="inlineStr"/>
-      <c r="W276" t="inlineStr"/>
-      <c r="X276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14567,24 +9679,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="inlineStr"/>
-      <c r="R277" t="inlineStr"/>
-      <c r="S277" t="inlineStr"/>
-      <c r="T277" t="inlineStr"/>
-      <c r="U277" t="inlineStr"/>
-      <c r="V277" t="inlineStr"/>
-      <c r="W277" t="inlineStr"/>
-      <c r="X277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14617,24 +9711,6 @@
           <t>watches</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr"/>
-      <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="inlineStr"/>
-      <c r="R278" t="inlineStr"/>
-      <c r="S278" t="inlineStr"/>
-      <c r="T278" t="inlineStr"/>
-      <c r="U278" t="inlineStr"/>
-      <c r="V278" t="inlineStr"/>
-      <c r="W278" t="inlineStr"/>
-      <c r="X278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14667,24 +9743,6 @@
           <t>jeans</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
-      <c r="R279" t="inlineStr"/>
-      <c r="S279" t="inlineStr"/>
-      <c r="T279" t="inlineStr"/>
-      <c r="U279" t="inlineStr"/>
-      <c r="V279" t="inlineStr"/>
-      <c r="W279" t="inlineStr"/>
-      <c r="X279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14697,36 +9755,16 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
-      <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
-      <c r="R280" t="inlineStr"/>
-      <c r="S280" t="inlineStr"/>
-      <c r="T280" t="inlineStr"/>
       <c r="U280" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V280" t="inlineStr"/>
-      <c r="W280" t="inlineStr"/>
-      <c r="X280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14739,36 +9777,16 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr"/>
-      <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="inlineStr"/>
-      <c r="R281" t="inlineStr"/>
-      <c r="S281" t="inlineStr"/>
-      <c r="T281" t="inlineStr"/>
       <c r="U281" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
-      <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14781,36 +9799,16 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
-      <c r="R282" t="inlineStr"/>
-      <c r="S282" t="inlineStr"/>
-      <c r="T282" t="inlineStr"/>
       <c r="U282" t="inlineStr">
         <is>
           <t>The Face</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
-      <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14823,36 +9821,16 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
-      <c r="R283" t="inlineStr"/>
-      <c r="S283" t="inlineStr"/>
-      <c r="T283" t="inlineStr"/>
       <c r="U283" t="inlineStr">
         <is>
           <t>The Face</t>
         </is>
       </c>
-      <c r="V283" t="inlineStr"/>
-      <c r="W283" t="inlineStr"/>
-      <c r="X283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14865,36 +9843,16 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
-      <c r="R284" t="inlineStr"/>
-      <c r="S284" t="inlineStr"/>
-      <c r="T284" t="inlineStr"/>
       <c r="U284" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V284" t="inlineStr"/>
-      <c r="W284" t="inlineStr"/>
-      <c r="X284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14907,36 +9865,16 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
-      <c r="R285" t="inlineStr"/>
-      <c r="S285" t="inlineStr"/>
-      <c r="T285" t="inlineStr"/>
       <c r="U285" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V285" t="inlineStr"/>
-      <c r="W285" t="inlineStr"/>
-      <c r="X285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14949,36 +9887,16 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
-      <c r="R286" t="inlineStr"/>
-      <c r="S286" t="inlineStr"/>
-      <c r="T286" t="inlineStr"/>
       <c r="U286" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V286" t="inlineStr"/>
-      <c r="W286" t="inlineStr"/>
-      <c r="X286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14991,36 +9909,16 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>edi</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
-      <c r="R287" t="inlineStr"/>
-      <c r="S287" t="inlineStr"/>
-      <c r="T287" t="inlineStr"/>
       <c r="U287" t="inlineStr">
         <is>
           <t>Vogue US</t>
         </is>
       </c>
-      <c r="V287" t="inlineStr"/>
-      <c r="W287" t="inlineStr"/>
-      <c r="X287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15033,7 +9931,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15054,23 +9951,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="inlineStr"/>
-      <c r="R288" t="inlineStr"/>
-      <c r="S288" t="inlineStr"/>
-      <c r="T288" t="inlineStr"/>
-      <c r="U288" t="inlineStr"/>
-      <c r="V288" t="inlineStr"/>
-      <c r="W288" t="inlineStr"/>
-      <c r="X288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15083,7 +9963,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15104,23 +9983,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
-      <c r="R289" t="inlineStr"/>
-      <c r="S289" t="inlineStr"/>
-      <c r="T289" t="inlineStr"/>
-      <c r="U289" t="inlineStr"/>
-      <c r="V289" t="inlineStr"/>
-      <c r="W289" t="inlineStr"/>
-      <c r="X289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15133,7 +9995,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15154,23 +10015,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
-      <c r="R290" t="inlineStr"/>
-      <c r="S290" t="inlineStr"/>
-      <c r="T290" t="inlineStr"/>
-      <c r="U290" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
-      <c r="W290" t="inlineStr"/>
-      <c r="X290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15183,7 +10027,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15204,23 +10047,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
-      <c r="R291" t="inlineStr"/>
-      <c r="S291" t="inlineStr"/>
-      <c r="T291" t="inlineStr"/>
-      <c r="U291" t="inlineStr"/>
-      <c r="V291" t="inlineStr"/>
-      <c r="W291" t="inlineStr"/>
-      <c r="X291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15233,7 +10059,6 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15254,23 +10079,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
-      <c r="R292" t="inlineStr"/>
-      <c r="S292" t="inlineStr"/>
-      <c r="T292" t="inlineStr"/>
-      <c r="U292" t="inlineStr"/>
-      <c r="V292" t="inlineStr"/>
-      <c r="W292" t="inlineStr"/>
-      <c r="X292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15283,7 +10091,6 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15304,23 +10111,6 @@
           <t>obsession</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
-      <c r="R293" t="inlineStr"/>
-      <c r="S293" t="inlineStr"/>
-      <c r="T293" t="inlineStr"/>
-      <c r="U293" t="inlineStr"/>
-      <c r="V293" t="inlineStr"/>
-      <c r="W293" t="inlineStr"/>
-      <c r="X293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15333,7 +10123,6 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15354,23 +10143,6 @@
           <t>obsession_formen</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr"/>
-      <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
-      <c r="R294" t="inlineStr"/>
-      <c r="S294" t="inlineStr"/>
-      <c r="T294" t="inlineStr"/>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
-      <c r="W294" t="inlineStr"/>
-      <c r="X294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15383,7 +10155,6 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15404,23 +10175,6 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
-      <c r="R295" t="inlineStr"/>
-      <c r="S295" t="inlineStr"/>
-      <c r="T295" t="inlineStr"/>
-      <c r="U295" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
-      <c r="W295" t="inlineStr"/>
-      <c r="X295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15433,7 +10187,6 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15454,23 +10207,6 @@
           <t>eternity</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
-      <c r="R296" t="inlineStr"/>
-      <c r="S296" t="inlineStr"/>
-      <c r="T296" t="inlineStr"/>
-      <c r="U296" t="inlineStr"/>
-      <c r="V296" t="inlineStr"/>
-      <c r="W296" t="inlineStr"/>
-      <c r="X296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15483,7 +10219,6 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>adv</t>
@@ -15504,23 +10239,757 @@
           <t>one</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
-      <c r="R297" t="inlineStr"/>
-      <c r="S297" t="inlineStr"/>
-      <c r="T297" t="inlineStr"/>
-      <c r="U297" t="inlineStr"/>
-      <c r="V297" t="inlineStr"/>
-      <c r="W297" t="inlineStr"/>
-      <c r="X297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1996_fw_adv_billboard_collection_ck_001</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>ck</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1999_ss_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2006_fw_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2006_fw_adv_billboard_underwear_001</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2006_ss_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2006_ss_adv_billboard_jeans_002</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2008_fw_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2009_fw_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2009_ss_adv_billboard_fragrance_secretobsession_001</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>fragrance</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>secretobsession</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2009_ss_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2009_ss_adv_billboard_underwear_001</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2010_ss_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2011_fw_adv_billboard_beauty_001</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2011_fw_adv_billboard_fragrance_ckone_001</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>fragrance</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ckone</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2011_ss_adv_billboard_underwear_001</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2012_ss_adv_billboard_swimwear_001</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>swimwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2012_ss_adv_billboard_underwear_001</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2013_fw_adv_billboard_collection_001</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2013_ss_adv_billboard_collection_001</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2015_fw_adv_billboard_jeans_001</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>billboard</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1992_fw_adv_print_underwear_001</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>print</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>underwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1993_fw_adv_print_jeans_001</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>print</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1996_fw_adv_print_jeans_001</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>print</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X406"/>
+  <dimension ref="A1:X425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13973,6 +13973,424 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1995_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2010_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2010_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2011_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2011_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2012_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2012_ss_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2013_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2013_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2014_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2014_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2015_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2015_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2016_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2016_fw_collection_menswear_001</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2017_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2018_ss_collection_001</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026_fw_collection_001</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>fw</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/archive_index.xlsx
+++ b/archive_index.xlsx
@@ -753,6 +753,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>brooke-shields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -780,6 +790,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>brooke-shields</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -839,6 +859,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>brooke-shields</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1001,6 +1031,11 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1028,6 +1063,11 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1055,6 +1095,11 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1082,6 +1127,11 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>richard-avedon</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1384,6 +1434,11 @@
           <t>underwear</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1438,6 +1493,11 @@
           <t>fragrance</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1470,6 +1530,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1701,6 +1766,11 @@
           <t>underwear</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1733,6 +1803,11 @@
           <t>underwear</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1765,6 +1840,11 @@
           <t>underwear</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1824,6 +1904,11 @@
           <t>obsession_formen</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1856,6 +1941,11 @@
           <t>obsession_formen</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1964,6 +2054,11 @@
           <t>underwear</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3409,6 +3504,16 @@
           <t>escape</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>mario-sorrenti</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3446,6 +3551,16 @@
           <t>escape_men</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>mario-sorrenti</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3483,6 +3598,16 @@
           <t>eternity</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>mario-sorrenti</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3520,6 +3645,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>mario-sorrenti</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -3991,6 +4121,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4023,6 +4163,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4055,6 +4205,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4087,6 +4247,16 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>kate-moss</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4124,6 +4294,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>kate-moss,karen-ferrari</t>
@@ -4272,6 +4447,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4304,6 +4484,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4336,6 +4521,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4368,6 +4558,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4400,6 +4595,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4432,6 +4632,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4469,6 +4674,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -4511,6 +4721,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -4553,6 +4768,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -4669,6 +4889,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4701,6 +4926,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4733,6 +4963,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4765,6 +5000,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4802,6 +5042,11 @@
           <t>menswear</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4839,6 +5084,11 @@
           <t>menswear</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5404,6 +5654,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5436,6 +5691,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5468,6 +5728,11 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5505,6 +5770,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -5547,6 +5817,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5584,6 +5859,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>kate-moss</t>
@@ -5626,6 +5906,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5663,6 +5948,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5700,6 +5990,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11083,6 +11378,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11115,6 +11420,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11147,6 +11462,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11179,6 +11504,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11211,6 +11546,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11243,6 +11588,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11275,6 +11630,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11307,6 +11672,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11339,6 +11714,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11371,6 +11756,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11403,6 +11798,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11435,6 +11840,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11467,6 +11882,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11499,6 +11924,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11531,6 +11966,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11563,6 +12008,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11595,6 +12050,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11627,6 +12092,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11659,6 +12134,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11691,6 +12176,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11723,6 +12218,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11755,6 +12260,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11787,6 +12302,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11819,6 +12344,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11851,6 +12386,16 @@
           <t>jeans</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>mikael-jansson</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>natalia-vodianova,jamie-dornan</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12891,6 +13436,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12923,6 +13473,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12955,6 +13510,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12987,6 +13547,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13019,6 +13584,11 @@
           <t>obsession_formen</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13051,6 +13621,11 @@
           <t>obsession</t>
         </is>
       </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13083,6 +13658,11 @@
           <t>obsession_formen</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13147,6 +13727,11 @@
           <t>eternity</t>
         </is>
       </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>bruce-weber</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13216,6 +13801,11 @@
           <t>ck</t>
         </is>
       </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>steven-meisel</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13896,6 +14486,16 @@
       <c r="F404" t="inlineStr">
         <is>
           <t>underwear</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>herb-ritts</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>kate-moss,mark-wahlberg</t>
         </is>
       </c>
     </row>
